--- a/output_plant/stomata_Intermediate_reichgelt_2020.xlsx
+++ b/output_plant/stomata_Intermediate_reichgelt_2020.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t>eDab</t>
   </si>
@@ -603,10 +603,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">9.09.50.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.5194/cp-16-1509-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-franks_reichgelt_2020.xlsx</t>
+    <t xml:space="preserve">stomata-franks_reichgelt_2020_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -615,12 +618,6 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Ar/Ar+Paleomag+varves; Age uncertainties reported in columns G and H are the min and max ages reported in Column W; actual uncertainties of ages in column W have not been determined.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09.50.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ar/Ar+Paleomag+varves</t>
   </si>
   <si>
@@ -799,6 +796,12 @@
   </si>
   <si>
     <t xml:space="preserve">84.43.68.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.4.16.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.4.16.1</t>
   </si>
 </sst>
 </file>
@@ -2099,18 +2102,20 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="B5" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>-45.527</v>
@@ -2119,85 +2124,171 @@
         <v>170.219</v>
       </c>
       <c r="H5" s="23" t="n">
-        <v>22.946</v>
+        <v>22.939</v>
       </c>
       <c r="I5" s="23"/>
-      <c r="J5" s="23" t="n">
-        <v>22.939</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>22.948</v>
-      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
       <c r="L5" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="24"/>
+        <v>201</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P5" s="24" t="n">
+        <v>172222222.2</v>
+      </c>
+      <c r="Q5" s="24" t="n">
+        <v>29397236.79</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="S5" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" s="24"/>
       <c r="U5" s="1"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
+      <c r="V5" s="24" t="n">
+        <v>0.00000798</v>
+      </c>
+      <c r="W5" s="24" t="n">
+        <v>0.00000153</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="24"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
+      <c r="AB5" s="24" t="n">
+        <v>0.00000518</v>
+      </c>
+      <c r="AC5" s="24" t="n">
+        <v>0.000000921</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="20"/>
-      <c r="AI5" s="20"/>
-      <c r="AJ5"/>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
-      <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
+      <c r="AH5" s="20" t="n">
+        <v>-28.193</v>
+      </c>
+      <c r="AI5" s="20" t="n">
+        <v>0.311437</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0.000714286</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AP5" s="23" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AQ5" s="23" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AR5" s="1"/>
-      <c r="AS5" s="1"/>
-      <c r="AT5" s="1"/>
-      <c r="AU5" s="1"/>
-      <c r="AV5" s="1"/>
-      <c r="AW5" s="1"/>
-      <c r="AX5" s="1"/>
-      <c r="AY5" s="1"/>
-      <c r="AZ5" s="1"/>
-      <c r="BA5" s="1"/>
-      <c r="BB5" s="1"/>
-      <c r="BC5" s="1"/>
-      <c r="BD5" s="1"/>
-      <c r="BE5" s="1"/>
-      <c r="BF5" s="1"/>
-      <c r="BG5" s="1"/>
-      <c r="BH5" s="1"/>
-      <c r="BI5" s="1"/>
-      <c r="BJ5" s="1"/>
+      <c r="AS5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="BE5" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF5" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH5" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BI5" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="BK5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>-45.527</v>
@@ -2206,31 +2297,29 @@
         <v>170.219</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>22.939</v>
+        <v>22.944</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
       <c r="L6" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="26" t="n">
+        <v>622222222.2</v>
+      </c>
+      <c r="Q6" s="26" t="n">
+        <v>40824829.05</v>
+      </c>
+      <c r="R6" t="s">
         <v>205</v>
-      </c>
-      <c r="P6" s="26" t="n">
-        <v>172222222.2</v>
-      </c>
-      <c r="Q6" s="26" t="n">
-        <v>29397236.79</v>
-      </c>
-      <c r="R6" t="s">
-        <v>206</v>
       </c>
       <c r="S6" s="24" t="n">
         <v>0</v>
@@ -2238,13 +2327,13 @@
       <c r="T6" s="24"/>
       <c r="U6"/>
       <c r="V6" s="26" t="n">
-        <v>0.00000798</v>
+        <v>0.0000336</v>
       </c>
       <c r="W6" s="26" t="n">
-        <v>0.00000153</v>
+        <v>0.0000245</v>
       </c>
       <c r="X6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y6" s="24" t="n">
         <v>0</v>
@@ -2254,13 +2343,13 @@
       </c>
       <c r="AA6"/>
       <c r="AB6" s="24" t="n">
-        <v>0.00000518</v>
+        <v>0.000003</v>
       </c>
       <c r="AC6" s="24" t="n">
-        <v>0.000000921</v>
+        <v>0.00000077</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE6" s="24" t="n">
         <v>0</v>
@@ -2270,13 +2359,13 @@
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="25" t="n">
-        <v>-28.193</v>
+        <v>-28.9795</v>
       </c>
       <c r="AI6" s="25" t="n">
-        <v>0.311437</v>
+        <v>0.4</v>
       </c>
       <c r="AJ6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK6" s="1" t="n">
         <v>400</v>
@@ -2285,13 +2374,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP6" s="23" t="n">
         <v>0.68</v>
@@ -2307,7 +2396,7 @@
         <v>0.1</v>
       </c>
       <c r="AU6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV6" s="1" t="n">
         <v>1</v>
@@ -2316,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="AX6" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY6" s="1" t="n">
         <v>1</v>
@@ -2325,7 +2414,7 @@
         <v>0.05</v>
       </c>
       <c r="BA6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB6" s="1" t="n">
         <v>1</v>
@@ -2334,7 +2423,7 @@
         <v>0.05</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE6" s="1" t="n">
         <v>0.2</v>
@@ -2343,7 +2432,7 @@
         <v>0.02</v>
       </c>
       <c r="BG6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH6" s="1" t="n">
         <v>0.013</v>
@@ -2352,25 +2441,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ6" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>-45.527</v>
@@ -2385,23 +2474,25 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
       <c r="L7" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O7" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="P7" s="26" t="n">
-        <v>622222222.2</v>
+        <v>159259259.3</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>40824829.05</v>
+        <v>42065987.75</v>
       </c>
       <c r="R7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S7" s="24" t="n">
         <v>0</v>
@@ -2409,13 +2500,13 @@
       <c r="T7" s="24"/>
       <c r="U7"/>
       <c r="V7" s="26" t="n">
-        <v>0.0000336</v>
+        <v>0.00000855</v>
       </c>
       <c r="W7" s="26" t="n">
-        <v>0.0000245</v>
+        <v>0.000000761</v>
       </c>
       <c r="X7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y7" s="24" t="n">
         <v>0</v>
@@ -2425,13 +2516,13 @@
       </c>
       <c r="AA7"/>
       <c r="AB7" s="24" t="n">
-        <v>0.000003</v>
+        <v>0.00000428</v>
       </c>
       <c r="AC7" s="24" t="n">
-        <v>0.00000077</v>
+        <v>0.0000009</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE7" s="24" t="n">
         <v>0</v>
@@ -2441,13 +2532,13 @@
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="25" t="n">
-        <v>-28.9795</v>
+        <v>-25.4182</v>
       </c>
       <c r="AI7" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK7" s="1" t="n">
         <v>400</v>
@@ -2456,13 +2547,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP7" s="23" t="n">
         <v>0.68</v>
@@ -2478,7 +2569,7 @@
         <v>0.1</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV7" s="1" t="n">
         <v>1</v>
@@ -2487,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY7" s="1" t="n">
         <v>1</v>
@@ -2496,7 +2587,7 @@
         <v>0.05</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB7" s="1" t="n">
         <v>1</v>
@@ -2505,7 +2596,7 @@
         <v>0.05</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE7" s="1" t="n">
         <v>0.2</v>
@@ -2514,7 +2605,7 @@
         <v>0.02</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH7" s="1" t="n">
         <v>0.013</v>
@@ -2523,7 +2614,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ7" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK7" s="1"/>
     </row>
@@ -2532,16 +2623,16 @@
         <v>215</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F8" s="25" t="n">
         <v>-45.527</v>
@@ -2556,25 +2647,23 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
       <c r="L8" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="26" t="n">
+        <v>343055555.6</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <v>56480397.25</v>
+      </c>
+      <c r="R8" t="s">
         <v>205</v>
-      </c>
-      <c r="P8" s="26" t="n">
-        <v>159259259.3</v>
-      </c>
-      <c r="Q8" s="26" t="n">
-        <v>42065987.75</v>
-      </c>
-      <c r="R8" t="s">
-        <v>206</v>
       </c>
       <c r="S8" s="24" t="n">
         <v>0</v>
@@ -2582,13 +2671,13 @@
       <c r="T8" s="24"/>
       <c r="U8"/>
       <c r="V8" s="26" t="n">
-        <v>0.00000855</v>
+        <v>0.000010375</v>
       </c>
       <c r="W8" s="26" t="n">
-        <v>0.000000761</v>
+        <v>0.00000522</v>
       </c>
       <c r="X8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="24" t="n">
         <v>0</v>
@@ -2598,13 +2687,13 @@
       </c>
       <c r="AA8"/>
       <c r="AB8" s="24" t="n">
-        <v>0.00000428</v>
+        <v>0.000001625</v>
       </c>
       <c r="AC8" s="24" t="n">
-        <v>0.0000009</v>
+        <v>0.000000873</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE8" s="24" t="n">
         <v>0</v>
@@ -2614,13 +2703,13 @@
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="25" t="n">
-        <v>-25.4182</v>
+        <v>-27.7113</v>
       </c>
       <c r="AI8" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK8" s="1" t="n">
         <v>400</v>
@@ -2629,13 +2718,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AO8" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP8" s="23" t="n">
         <v>0.68</v>
@@ -2651,7 +2740,7 @@
         <v>0.1</v>
       </c>
       <c r="AU8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV8" s="1" t="n">
         <v>1</v>
@@ -2660,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AX8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY8" s="1" t="n">
         <v>1</v>
@@ -2669,7 +2758,7 @@
         <v>0.05</v>
       </c>
       <c r="BA8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB8" s="1" t="n">
         <v>1</v>
@@ -2678,7 +2767,7 @@
         <v>0.05</v>
       </c>
       <c r="BD8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE8" s="1" t="n">
         <v>0.2</v>
@@ -2687,7 +2776,7 @@
         <v>0.02</v>
       </c>
       <c r="BG8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH8" s="1" t="n">
         <v>0.013</v>
@@ -2696,7 +2785,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ8" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK8" s="1"/>
     </row>
@@ -2705,16 +2794,16 @@
         <v>216</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>-45.527</v>
@@ -2723,29 +2812,31 @@
         <v>170.219</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>22.944</v>
+        <v>22.947</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
       <c r="L9" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="O9" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="P9" s="26" t="n">
-        <v>343055555.6</v>
+        <v>582400000</v>
       </c>
       <c r="Q9" s="26" t="n">
-        <v>56480397.25</v>
+        <v>132713224.7</v>
       </c>
       <c r="R9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S9" s="24" t="n">
         <v>0</v>
@@ -2753,13 +2844,13 @@
       <c r="T9" s="24"/>
       <c r="U9"/>
       <c r="V9" s="26" t="n">
-        <v>0.000010375</v>
+        <v>0.0000116</v>
       </c>
       <c r="W9" s="26" t="n">
-        <v>0.00000522</v>
+        <v>0.00000517</v>
       </c>
       <c r="X9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y9" s="24" t="n">
         <v>0</v>
@@ -2769,13 +2860,13 @@
       </c>
       <c r="AA9"/>
       <c r="AB9" s="24" t="n">
-        <v>0.000001625</v>
+        <v>0.0000026</v>
       </c>
       <c r="AC9" s="24" t="n">
-        <v>0.000000873</v>
+        <v>0.00000139</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE9" s="24" t="n">
         <v>0</v>
@@ -2785,13 +2876,13 @@
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="25" t="n">
-        <v>-27.7113</v>
+        <v>-28.6888</v>
       </c>
       <c r="AI9" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK9" s="1" t="n">
         <v>400</v>
@@ -2800,13 +2891,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO9" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP9" s="23" t="n">
         <v>0.68</v>
@@ -2822,7 +2913,7 @@
         <v>0.1</v>
       </c>
       <c r="AU9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV9" s="1" t="n">
         <v>1</v>
@@ -2831,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="AX9" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY9" s="1" t="n">
         <v>1</v>
@@ -2840,7 +2931,7 @@
         <v>0.05</v>
       </c>
       <c r="BA9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB9" s="1" t="n">
         <v>1</v>
@@ -2849,7 +2940,7 @@
         <v>0.05</v>
       </c>
       <c r="BD9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE9" s="1" t="n">
         <v>0.2</v>
@@ -2858,7 +2949,7 @@
         <v>0.02</v>
       </c>
       <c r="BG9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH9" s="1" t="n">
         <v>0.013</v>
@@ -2867,25 +2958,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ9" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F10" s="25" t="n">
         <v>-45.527</v>
@@ -2900,25 +2991,25 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
       <c r="L10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="N10" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="P10" s="26" t="n">
-        <v>582400000</v>
+        <v>280000000</v>
       </c>
       <c r="Q10" s="26" t="n">
-        <v>132713224.7</v>
+        <v>28760398.01</v>
       </c>
       <c r="R10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S10" s="24" t="n">
         <v>0</v>
@@ -2926,13 +3017,13 @@
       <c r="T10" s="24"/>
       <c r="U10"/>
       <c r="V10" s="26" t="n">
-        <v>0.0000116</v>
+        <v>0.00000691</v>
       </c>
       <c r="W10" s="26" t="n">
-        <v>0.00000517</v>
+        <v>0.00000109</v>
       </c>
       <c r="X10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y10" s="24" t="n">
         <v>0</v>
@@ -2942,13 +3033,13 @@
       </c>
       <c r="AA10"/>
       <c r="AB10" s="24" t="n">
-        <v>0.0000026</v>
+        <v>0.00000463</v>
       </c>
       <c r="AC10" s="24" t="n">
-        <v>0.00000139</v>
+        <v>0.000000822</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE10" s="24" t="n">
         <v>0</v>
@@ -2958,13 +3049,13 @@
       </c>
       <c r="AG10" s="1"/>
       <c r="AH10" s="25" t="n">
-        <v>-28.6888</v>
+        <v>-29.5275</v>
       </c>
       <c r="AI10" s="25" t="n">
-        <v>0.4</v>
+        <v>0.154375</v>
       </c>
       <c r="AJ10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK10" s="1" t="n">
         <v>400</v>
@@ -2979,7 +3070,7 @@
         <v>1.22</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP10" s="23" t="n">
         <v>0.68</v>
@@ -2995,7 +3086,7 @@
         <v>0.1</v>
       </c>
       <c r="AU10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV10" s="1" t="n">
         <v>1</v>
@@ -3004,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="AX10" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY10" s="1" t="n">
         <v>1</v>
@@ -3013,7 +3104,7 @@
         <v>0.05</v>
       </c>
       <c r="BA10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB10" s="1" t="n">
         <v>1</v>
@@ -3022,7 +3113,7 @@
         <v>0.05</v>
       </c>
       <c r="BD10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>0.2</v>
@@ -3031,7 +3122,7 @@
         <v>0.02</v>
       </c>
       <c r="BG10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH10" s="1" t="n">
         <v>0.013</v>
@@ -3040,7 +3131,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ10" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK10" s="1"/>
     </row>
@@ -3049,16 +3140,16 @@
         <v>220</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>-45.527</v>
@@ -3073,25 +3164,25 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="26" t="n">
+        <v>186666666.7</v>
+      </c>
+      <c r="Q11" s="26" t="n">
+        <v>64978628.97</v>
+      </c>
+      <c r="R11" t="s">
         <v>205</v>
-      </c>
-      <c r="P11" s="26" t="n">
-        <v>280000000</v>
-      </c>
-      <c r="Q11" s="26" t="n">
-        <v>28760398.01</v>
-      </c>
-      <c r="R11" t="s">
-        <v>206</v>
       </c>
       <c r="S11" s="24" t="n">
         <v>0</v>
@@ -3099,13 +3190,13 @@
       <c r="T11" s="24"/>
       <c r="U11"/>
       <c r="V11" s="26" t="n">
-        <v>0.00000691</v>
+        <v>0.00000797</v>
       </c>
       <c r="W11" s="26" t="n">
-        <v>0.00000109</v>
+        <v>0.000000855</v>
       </c>
       <c r="X11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y11" s="24" t="n">
         <v>0</v>
@@ -3115,13 +3206,13 @@
       </c>
       <c r="AA11"/>
       <c r="AB11" s="24" t="n">
-        <v>0.00000463</v>
+        <v>0.0000042</v>
       </c>
       <c r="AC11" s="24" t="n">
-        <v>0.000000822</v>
+        <v>0.000000891</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE11" s="24" t="n">
         <v>0</v>
@@ -3131,13 +3222,13 @@
       </c>
       <c r="AG11" s="1"/>
       <c r="AH11" s="25" t="n">
-        <v>-29.5275</v>
+        <v>-27.1359</v>
       </c>
       <c r="AI11" s="25" t="n">
-        <v>0.154375</v>
+        <v>0.4</v>
       </c>
       <c r="AJ11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK11" s="1" t="n">
         <v>400</v>
@@ -3152,7 +3243,7 @@
         <v>1.22</v>
       </c>
       <c r="AO11" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP11" s="23" t="n">
         <v>0.68</v>
@@ -3168,7 +3259,7 @@
         <v>0.1</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV11" s="1" t="n">
         <v>1</v>
@@ -3177,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AX11" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY11" s="1" t="n">
         <v>1</v>
@@ -3186,7 +3277,7 @@
         <v>0.05</v>
       </c>
       <c r="BA11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB11" s="1" t="n">
         <v>1</v>
@@ -3195,7 +3286,7 @@
         <v>0.05</v>
       </c>
       <c r="BD11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE11" s="1" t="n">
         <v>0.2</v>
@@ -3204,7 +3295,7 @@
         <v>0.02</v>
       </c>
       <c r="BG11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH11" s="1" t="n">
         <v>0.013</v>
@@ -3213,7 +3304,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ11" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK11" s="1"/>
     </row>
@@ -3222,16 +3313,16 @@
         <v>221</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F12" s="25" t="n">
         <v>-45.527</v>
@@ -3246,25 +3337,25 @@
       <c r="J12" s="23"/>
       <c r="K12" s="23"/>
       <c r="L12" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="26" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="Q12" s="26" t="n">
+        <v>23040490.39</v>
+      </c>
+      <c r="R12" t="s">
         <v>205</v>
-      </c>
-      <c r="P12" s="26" t="n">
-        <v>186666666.7</v>
-      </c>
-      <c r="Q12" s="26" t="n">
-        <v>64978628.97</v>
-      </c>
-      <c r="R12" t="s">
-        <v>206</v>
       </c>
       <c r="S12" s="24" t="n">
         <v>0</v>
@@ -3272,13 +3363,13 @@
       <c r="T12" s="24"/>
       <c r="U12"/>
       <c r="V12" s="26" t="n">
-        <v>0.00000797</v>
+        <v>0.0000086</v>
       </c>
       <c r="W12" s="26" t="n">
-        <v>0.000000855</v>
+        <v>0.00000259</v>
       </c>
       <c r="X12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y12" s="24" t="n">
         <v>0</v>
@@ -3288,13 +3379,13 @@
       </c>
       <c r="AA12"/>
       <c r="AB12" s="24" t="n">
-        <v>0.0000042</v>
+        <v>0.0000024</v>
       </c>
       <c r="AC12" s="24" t="n">
-        <v>0.000000891</v>
+        <v>0.00000106</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE12" s="24" t="n">
         <v>0</v>
@@ -3304,13 +3395,13 @@
       </c>
       <c r="AG12" s="1"/>
       <c r="AH12" s="25" t="n">
-        <v>-27.1359</v>
+        <v>-26.258</v>
       </c>
       <c r="AI12" s="25" t="n">
-        <v>0.4</v>
+        <v>0.151497</v>
       </c>
       <c r="AJ12" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK12" s="1" t="n">
         <v>400</v>
@@ -3325,7 +3416,7 @@
         <v>1.22</v>
       </c>
       <c r="AO12" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP12" s="23" t="n">
         <v>0.68</v>
@@ -3341,7 +3432,7 @@
         <v>0.1</v>
       </c>
       <c r="AU12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV12" s="1" t="n">
         <v>1</v>
@@ -3350,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="AX12" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY12" s="1" t="n">
         <v>1</v>
@@ -3359,7 +3450,7 @@
         <v>0.05</v>
       </c>
       <c r="BA12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB12" s="1" t="n">
         <v>1</v>
@@ -3368,7 +3459,7 @@
         <v>0.05</v>
       </c>
       <c r="BD12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE12" s="1" t="n">
         <v>0.2</v>
@@ -3377,7 +3468,7 @@
         <v>0.02</v>
       </c>
       <c r="BG12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH12" s="1" t="n">
         <v>0.013</v>
@@ -3386,7 +3477,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK12" s="1"/>
     </row>
@@ -3395,16 +3486,16 @@
         <v>222</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>-45.527</v>
@@ -3419,25 +3510,25 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
       <c r="L13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="26" t="n">
+        <v>153333333.3</v>
+      </c>
+      <c r="Q13" s="26" t="n">
+        <v>32773069.34</v>
+      </c>
+      <c r="R13" t="s">
         <v>205</v>
-      </c>
-      <c r="P13" s="26" t="n">
-        <v>240000000</v>
-      </c>
-      <c r="Q13" s="26" t="n">
-        <v>23040490.39</v>
-      </c>
-      <c r="R13" t="s">
-        <v>206</v>
       </c>
       <c r="S13" s="24" t="n">
         <v>0</v>
@@ -3445,13 +3536,13 @@
       <c r="T13" s="24"/>
       <c r="U13"/>
       <c r="V13" s="26" t="n">
-        <v>0.0000086</v>
+        <v>0.0000102</v>
       </c>
       <c r="W13" s="26" t="n">
-        <v>0.00000259</v>
+        <v>0.00000505</v>
       </c>
       <c r="X13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y13" s="24" t="n">
         <v>0</v>
@@ -3461,13 +3552,13 @@
       </c>
       <c r="AA13"/>
       <c r="AB13" s="24" t="n">
-        <v>0.0000024</v>
+        <v>0.000002</v>
       </c>
       <c r="AC13" s="24" t="n">
-        <v>0.00000106</v>
+        <v>0.000000664</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE13" s="24" t="n">
         <v>0</v>
@@ -3477,13 +3568,13 @@
       </c>
       <c r="AG13" s="1"/>
       <c r="AH13" s="25" t="n">
-        <v>-26.258</v>
+        <v>-28.1399</v>
       </c>
       <c r="AI13" s="25" t="n">
-        <v>0.151497</v>
+        <v>0.4</v>
       </c>
       <c r="AJ13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK13" s="1" t="n">
         <v>400</v>
@@ -3498,7 +3589,7 @@
         <v>1.22</v>
       </c>
       <c r="AO13" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP13" s="23" t="n">
         <v>0.68</v>
@@ -3514,7 +3605,7 @@
         <v>0.1</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV13" s="1" t="n">
         <v>1</v>
@@ -3523,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AX13" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY13" s="1" t="n">
         <v>1</v>
@@ -3532,7 +3623,7 @@
         <v>0.05</v>
       </c>
       <c r="BA13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB13" s="1" t="n">
         <v>1</v>
@@ -3541,7 +3632,7 @@
         <v>0.05</v>
       </c>
       <c r="BD13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE13" s="1" t="n">
         <v>0.2</v>
@@ -3550,7 +3641,7 @@
         <v>0.02</v>
       </c>
       <c r="BG13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH13" s="1" t="n">
         <v>0.013</v>
@@ -3559,7 +3650,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK13" s="1"/>
     </row>
@@ -3568,16 +3659,16 @@
         <v>223</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F14" s="25" t="n">
         <v>-45.527</v>
@@ -3586,31 +3677,29 @@
         <v>170.219</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>22.947</v>
+        <v>22.948</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
       <c r="K14" s="23"/>
       <c r="L14" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O14" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="26" t="n">
+        <v>517866666.7</v>
+      </c>
+      <c r="Q14" s="26" t="n">
+        <v>131215175.3</v>
+      </c>
+      <c r="R14" t="s">
         <v>205</v>
-      </c>
-      <c r="P14" s="26" t="n">
-        <v>153333333.3</v>
-      </c>
-      <c r="Q14" s="26" t="n">
-        <v>32773069.34</v>
-      </c>
-      <c r="R14" t="s">
-        <v>206</v>
       </c>
       <c r="S14" s="24" t="n">
         <v>0</v>
@@ -3621,10 +3710,10 @@
         <v>0.0000102</v>
       </c>
       <c r="W14" s="26" t="n">
-        <v>0.00000505</v>
+        <v>0.00000461</v>
       </c>
       <c r="X14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y14" s="24" t="n">
         <v>0</v>
@@ -3634,13 +3723,13 @@
       </c>
       <c r="AA14"/>
       <c r="AB14" s="24" t="n">
-        <v>0.000002</v>
+        <v>0.0000022</v>
       </c>
       <c r="AC14" s="24" t="n">
-        <v>0.000000664</v>
+        <v>0.0000015</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE14" s="24" t="n">
         <v>0</v>
@@ -3650,13 +3739,13 @@
       </c>
       <c r="AG14" s="1"/>
       <c r="AH14" s="25" t="n">
-        <v>-28.1399</v>
+        <v>-29.373</v>
       </c>
       <c r="AI14" s="25" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK14" s="1" t="n">
         <v>400</v>
@@ -3665,13 +3754,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP14" s="23" t="n">
         <v>0.68</v>
@@ -3687,7 +3776,7 @@
         <v>0.1</v>
       </c>
       <c r="AU14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV14" s="1" t="n">
         <v>1</v>
@@ -3696,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="AX14" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY14" s="1" t="n">
         <v>1</v>
@@ -3705,7 +3794,7 @@
         <v>0.05</v>
       </c>
       <c r="BA14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB14" s="1" t="n">
         <v>1</v>
@@ -3714,7 +3803,7 @@
         <v>0.05</v>
       </c>
       <c r="BD14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE14" s="1" t="n">
         <v>0.2</v>
@@ -3723,7 +3812,7 @@
         <v>0.02</v>
       </c>
       <c r="BG14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH14" s="1" t="n">
         <v>0.013</v>
@@ -3732,7 +3821,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ14" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK14" s="1"/>
     </row>
@@ -3741,16 +3830,16 @@
         <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F15" t="n">
         <v>-45.527</v>
@@ -3765,23 +3854,25 @@
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
       <c r="L15" t="s">
+        <v>201</v>
+      </c>
+      <c r="M15" t="s">
         <v>202</v>
       </c>
-      <c r="M15" t="s">
-        <v>213</v>
-      </c>
       <c r="N15" t="s">
-        <v>213</v>
-      </c>
-      <c r="O15"/>
+        <v>203</v>
+      </c>
+      <c r="O15" t="s">
+        <v>204</v>
+      </c>
       <c r="P15" t="n">
-        <v>517866666.7</v>
+        <v>148148148.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>131215175.3</v>
+        <v>23129622.22</v>
       </c>
       <c r="R15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3789,13 +3880,13 @@
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15" t="n">
-        <v>0.0000102</v>
+        <v>0.00000967</v>
       </c>
       <c r="W15" t="n">
-        <v>0.00000461</v>
+        <v>0.00000323</v>
       </c>
       <c r="X15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -3805,13 +3896,13 @@
       </c>
       <c r="AA15"/>
       <c r="AB15" t="n">
-        <v>0.0000022</v>
+        <v>0.000002</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0000015</v>
+        <v>0.000000881</v>
       </c>
       <c r="AD15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -3821,13 +3912,13 @@
       </c>
       <c r="AG15"/>
       <c r="AH15" t="n">
-        <v>-29.373</v>
+        <v>-27.3376</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.4</v>
+        <v>0.317969</v>
       </c>
       <c r="AJ15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK15" t="n">
         <v>400</v>
@@ -3836,13 +3927,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP15" t="n">
         <v>0.68</v>
@@ -3858,7 +3949,7 @@
         <v>0.1</v>
       </c>
       <c r="AU15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV15" t="n">
         <v>1</v>
@@ -3867,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="AX15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY15" t="n">
         <v>1</v>
@@ -3876,7 +3967,7 @@
         <v>0.05</v>
       </c>
       <c r="BA15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB15" t="n">
         <v>1</v>
@@ -3885,7 +3976,7 @@
         <v>0.05</v>
       </c>
       <c r="BD15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE15" t="n">
         <v>0.2</v>
@@ -3894,7 +3985,7 @@
         <v>0.02</v>
       </c>
       <c r="BG15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH15" t="n">
         <v>0.013</v>
@@ -3903,7 +3994,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK15" s="1"/>
     </row>
@@ -3912,16 +4003,16 @@
         <v>225</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
         <v>-45.527</v>
@@ -3936,25 +4027,25 @@
       <c r="J16" s="23"/>
       <c r="K16" s="23"/>
       <c r="L16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s">
+        <v>217</v>
+      </c>
+      <c r="N16" t="s">
         <v>203</v>
       </c>
-      <c r="N16" t="s">
-        <v>204</v>
-      </c>
       <c r="O16" t="s">
+        <v>218</v>
+      </c>
+      <c r="P16" t="n">
+        <v>524533333.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>78341323.47</v>
+      </c>
+      <c r="R16" t="s">
         <v>205</v>
-      </c>
-      <c r="P16" t="n">
-        <v>148148148.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>23129622.22</v>
-      </c>
-      <c r="R16" t="s">
-        <v>206</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3962,13 +4053,13 @@
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16" t="n">
-        <v>0.00000967</v>
+        <v>0.0000085</v>
       </c>
       <c r="W16" t="n">
-        <v>0.00000323</v>
+        <v>0.00000318</v>
       </c>
       <c r="X16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -3978,13 +4069,13 @@
       </c>
       <c r="AA16"/>
       <c r="AB16" t="n">
-        <v>0.000002</v>
+        <v>0.00000167</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.000000881</v>
+        <v>0.000000837</v>
       </c>
       <c r="AD16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3994,13 +4085,13 @@
       </c>
       <c r="AG16"/>
       <c r="AH16" t="n">
-        <v>-27.3376</v>
+        <v>-31.2999</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.317969</v>
+        <v>0.520354</v>
       </c>
       <c r="AJ16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK16" t="n">
         <v>400</v>
@@ -4015,7 +4106,7 @@
         <v>1.22</v>
       </c>
       <c r="AO16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP16" t="n">
         <v>0.68</v>
@@ -4031,7 +4122,7 @@
         <v>0.1</v>
       </c>
       <c r="AU16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
@@ -4040,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="AX16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
@@ -4049,7 +4140,7 @@
         <v>0.05</v>
       </c>
       <c r="BA16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB16" t="n">
         <v>1</v>
@@ -4058,7 +4149,7 @@
         <v>0.05</v>
       </c>
       <c r="BD16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE16" t="n">
         <v>0.2</v>
@@ -4067,7 +4158,7 @@
         <v>0.02</v>
       </c>
       <c r="BG16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH16" t="n">
         <v>0.013</v>
@@ -4076,7 +4167,7 @@
         <v>0.005</v>
       </c>
       <c r="BJ16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK16" s="1"/>
     </row>
@@ -4085,16 +4176,16 @@
         <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F17" t="n">
         <v>-45.527</v>
@@ -4109,25 +4200,23 @@
       <c r="J17" s="23"/>
       <c r="K17" s="23"/>
       <c r="L17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="N17" t="s">
-        <v>204</v>
-      </c>
-      <c r="O17" t="s">
-        <v>219</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O17"/>
       <c r="P17" t="n">
-        <v>524533333.3</v>
+        <v>422222222.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>78341323.47</v>
+        <v>54433105.4</v>
       </c>
       <c r="R17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4135,13 +4224,13 @@
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17" t="n">
-        <v>0.0000085</v>
+        <v>0.0000115</v>
       </c>
       <c r="W17" t="n">
-        <v>0.00000318</v>
+        <v>0.00000323</v>
       </c>
       <c r="X17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -4151,13 +4240,13 @@
       </c>
       <c r="AA17"/>
       <c r="AB17" t="n">
-        <v>0.00000167</v>
+        <v>0.00000275</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.000000837</v>
+        <v>0.00000129</v>
       </c>
       <c r="AD17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -4167,13 +4256,13 @@
       </c>
       <c r="AG17"/>
       <c r="AH17" t="n">
-        <v>-31.2999</v>
+        <v>-27.7407</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.520354</v>
+        <v>0.293212</v>
       </c>
       <c r="AJ17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK17" t="n">
         <v>400</v>
@@ -4182,13 +4271,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM17" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AO17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="n">
         <v>0.68</v>
@@ -4204,7 +4293,7 @@
         <v>0.1</v>
       </c>
       <c r="AU17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
@@ -4213,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="AX17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -4222,7 +4311,7 @@
         <v>0.05</v>
       </c>
       <c r="BA17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB17" t="n">
         <v>1</v>
@@ -4231,7 +4320,7 @@
         <v>0.05</v>
       </c>
       <c r="BD17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE17" t="n">
         <v>0.2</v>
@@ -4240,7 +4329,7 @@
         <v>0.02</v>
       </c>
       <c r="BG17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH17" t="n">
         <v>0.013</v>
@@ -4249,23 +4338,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK17" s="1"/>
     </row>
     <row r="18">
-      <c r="A18"/>
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
       <c r="B18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F18" t="n">
         <v>-45.527</v>
@@ -4274,85 +4365,171 @@
         <v>170.219</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>22.968</v>
+        <v>22.961</v>
       </c>
       <c r="I18" s="23"/>
-      <c r="J18" s="23" t="n">
-        <v>22.961</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>22.972</v>
-      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
       <c r="L18" t="s">
-        <v>200</v>
-      </c>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18"/>
-      <c r="S18"/>
+        <v>201</v>
+      </c>
+      <c r="M18" t="s">
+        <v>202</v>
+      </c>
+      <c r="N18" t="s">
+        <v>203</v>
+      </c>
+      <c r="O18" t="s">
+        <v>204</v>
+      </c>
+      <c r="P18" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>25337231.67</v>
+      </c>
+      <c r="R18" t="s">
+        <v>205</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
       <c r="T18"/>
       <c r="U18"/>
-      <c r="V18"/>
-      <c r="W18"/>
-      <c r="X18"/>
-      <c r="Y18"/>
-      <c r="Z18"/>
+      <c r="V18" t="n">
+        <v>0.00000905</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.00000101</v>
+      </c>
+      <c r="X18" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
       <c r="AA18"/>
-      <c r="AB18"/>
-      <c r="AC18"/>
-      <c r="AD18"/>
-      <c r="AE18"/>
-      <c r="AF18"/>
+      <c r="AB18" t="n">
+        <v>0.00000487</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.000000995</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>206</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
       <c r="AG18"/>
-      <c r="AH18"/>
-      <c r="AI18"/>
-      <c r="AJ18"/>
-      <c r="AK18"/>
-      <c r="AL18"/>
-      <c r="AM18"/>
-      <c r="AN18"/>
-      <c r="AO18"/>
-      <c r="AP18"/>
-      <c r="AQ18"/>
+      <c r="AH18" t="n">
+        <v>-25.6937</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>400</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.000714286</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>208</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AR18"/>
-      <c r="AS18"/>
-      <c r="AT18"/>
-      <c r="AU18"/>
-      <c r="AV18"/>
-      <c r="AW18"/>
-      <c r="AX18"/>
-      <c r="AY18"/>
-      <c r="AZ18"/>
-      <c r="BA18"/>
-      <c r="BB18"/>
-      <c r="BC18"/>
-      <c r="BD18"/>
-      <c r="BE18"/>
-      <c r="BF18"/>
-      <c r="BG18"/>
-      <c r="BH18"/>
-      <c r="BI18"/>
-      <c r="BJ18"/>
+      <c r="AS18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>209</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>209</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>209</v>
+      </c>
       <c r="BK18" s="1"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F19" t="n">
         <v>-45.527</v>
@@ -4361,29 +4538,31 @@
         <v>170.219</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>22.948</v>
+        <v>22.961</v>
       </c>
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
       <c r="K19" s="23"/>
       <c r="L19" t="s">
+        <v>201</v>
+      </c>
+      <c r="M19" t="s">
         <v>202</v>
       </c>
-      <c r="M19" t="s">
-        <v>213</v>
-      </c>
       <c r="N19" t="s">
-        <v>213</v>
-      </c>
-      <c r="O19"/>
+        <v>203</v>
+      </c>
+      <c r="O19" t="s">
+        <v>204</v>
+      </c>
       <c r="P19" t="n">
-        <v>422222222.2</v>
+        <v>220634920.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>54433105.4</v>
+        <v>90818992.28</v>
       </c>
       <c r="R19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4391,13 +4570,13 @@
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19" t="n">
-        <v>0.0000115</v>
+        <v>0.0000161</v>
       </c>
       <c r="W19" t="n">
-        <v>0.00000323</v>
+        <v>0.00000702</v>
       </c>
       <c r="X19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -4407,13 +4586,13 @@
       </c>
       <c r="AA19"/>
       <c r="AB19" t="n">
-        <v>0.00000275</v>
+        <v>0.00000229</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.00000129</v>
+        <v>0.00000114</v>
       </c>
       <c r="AD19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -4423,13 +4602,13 @@
       </c>
       <c r="AG19"/>
       <c r="AH19" t="n">
-        <v>-27.7407</v>
+        <v>-29.8075</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.293212</v>
+        <v>0.4</v>
       </c>
       <c r="AJ19" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK19" t="n">
         <v>400</v>
@@ -4438,13 +4617,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM19" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP19" t="n">
         <v>0.68</v>
@@ -4460,7 +4639,7 @@
         <v>0.1</v>
       </c>
       <c r="AU19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV19" t="n">
         <v>1</v>
@@ -4469,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="AX19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY19" t="n">
         <v>1</v>
@@ -4478,7 +4657,7 @@
         <v>0.05</v>
       </c>
       <c r="BA19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB19" t="n">
         <v>1</v>
@@ -4487,7 +4666,7 @@
         <v>0.05</v>
       </c>
       <c r="BD19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE19" t="n">
         <v>0.2</v>
@@ -4496,7 +4675,7 @@
         <v>0.02</v>
       </c>
       <c r="BG19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH19" t="n">
         <v>0.013</v>
@@ -4505,25 +4684,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F20" t="n">
         <v>-45.527</v>
@@ -4538,25 +4717,25 @@
       <c r="J20" s="23"/>
       <c r="K20" s="23"/>
       <c r="L20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s">
+        <v>217</v>
+      </c>
+      <c r="N20" t="s">
         <v>203</v>
       </c>
-      <c r="N20" t="s">
-        <v>204</v>
-      </c>
       <c r="O20" t="s">
+        <v>218</v>
+      </c>
+      <c r="P20" t="n">
+        <v>351851851.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>53364188.61</v>
+      </c>
+      <c r="R20" t="s">
         <v>205</v>
-      </c>
-      <c r="P20" t="n">
-        <v>220000000</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>25337231.67</v>
-      </c>
-      <c r="R20" t="s">
-        <v>206</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4564,13 +4743,13 @@
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20" t="n">
-        <v>0.00000905</v>
+        <v>0.0000107</v>
       </c>
       <c r="W20" t="n">
-        <v>0.00000101</v>
+        <v>0.00000535</v>
       </c>
       <c r="X20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -4580,13 +4759,13 @@
       </c>
       <c r="AA20"/>
       <c r="AB20" t="n">
-        <v>0.00000487</v>
+        <v>0.00000267</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.000000995</v>
+        <v>0.0000012</v>
       </c>
       <c r="AD20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -4596,13 +4775,13 @@
       </c>
       <c r="AG20"/>
       <c r="AH20" t="n">
-        <v>-25.6937</v>
+        <v>-27.3921</v>
       </c>
       <c r="AI20" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK20" t="n">
         <v>400</v>
@@ -4617,7 +4796,7 @@
         <v>1.22</v>
       </c>
       <c r="AO20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP20" t="n">
         <v>0.68</v>
@@ -4633,7 +4812,7 @@
         <v>0.1</v>
       </c>
       <c r="AU20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV20" t="n">
         <v>1</v>
@@ -4642,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="AX20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
@@ -4651,7 +4830,7 @@
         <v>0.05</v>
       </c>
       <c r="BA20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB20" t="n">
         <v>1</v>
@@ -4660,7 +4839,7 @@
         <v>0.05</v>
       </c>
       <c r="BD20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE20" t="n">
         <v>0.2</v>
@@ -4669,7 +4848,7 @@
         <v>0.02</v>
       </c>
       <c r="BG20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH20" t="n">
         <v>0.013</v>
@@ -4678,25 +4857,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK20" s="1"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F21" t="n">
         <v>-45.527</v>
@@ -4705,31 +4884,31 @@
         <v>170.219</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>22.961</v>
+        <v>22.962</v>
       </c>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
       <c r="L21" t="s">
+        <v>201</v>
+      </c>
+      <c r="M21" t="s">
         <v>202</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>203</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>204</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="n">
+        <v>153333333.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>22771001.7</v>
+      </c>
+      <c r="R21" t="s">
         <v>205</v>
-      </c>
-      <c r="P21" t="n">
-        <v>220634920.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>90818992.28</v>
-      </c>
-      <c r="R21" t="s">
-        <v>206</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4737,13 +4916,13 @@
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21" t="n">
-        <v>0.0000161</v>
+        <v>0.00000897</v>
       </c>
       <c r="W21" t="n">
-        <v>0.00000702</v>
+        <v>0.00000102</v>
       </c>
       <c r="X21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -4753,13 +4932,13 @@
       </c>
       <c r="AA21"/>
       <c r="AB21" t="n">
-        <v>0.00000229</v>
+        <v>0.00000453</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.00000114</v>
+        <v>0.000000742</v>
       </c>
       <c r="AD21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4769,13 +4948,13 @@
       </c>
       <c r="AG21"/>
       <c r="AH21" t="n">
-        <v>-29.8075</v>
+        <v>-28.4748</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.4</v>
+        <v>0.293647</v>
       </c>
       <c r="AJ21" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK21" t="n">
         <v>400</v>
@@ -4790,7 +4969,7 @@
         <v>1.22</v>
       </c>
       <c r="AO21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP21" t="n">
         <v>0.68</v>
@@ -4806,7 +4985,7 @@
         <v>0.1</v>
       </c>
       <c r="AU21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4815,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="AX21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY21" t="n">
         <v>1</v>
@@ -4824,7 +5003,7 @@
         <v>0.05</v>
       </c>
       <c r="BA21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB21" t="n">
         <v>1</v>
@@ -4833,7 +5012,7 @@
         <v>0.05</v>
       </c>
       <c r="BD21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE21" t="n">
         <v>0.2</v>
@@ -4842,7 +5021,7 @@
         <v>0.02</v>
       </c>
       <c r="BG21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH21" t="n">
         <v>0.013</v>
@@ -4851,25 +5030,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK21" s="1"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F22" t="n">
         <v>-45.527</v>
@@ -4878,31 +5057,31 @@
         <v>170.219</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>22.961</v>
+        <v>22.962</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
       <c r="L22" t="s">
+        <v>201</v>
+      </c>
+      <c r="M22" t="s">
         <v>202</v>
       </c>
-      <c r="M22" t="s">
-        <v>218</v>
-      </c>
       <c r="N22" t="s">
+        <v>203</v>
+      </c>
+      <c r="O22" t="s">
         <v>204</v>
       </c>
-      <c r="O22" t="s">
-        <v>219</v>
-      </c>
       <c r="P22" t="n">
-        <v>351851851.9</v>
+        <v>206666666.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>53364188.61</v>
+        <v>37350525.14</v>
       </c>
       <c r="R22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4910,13 +5089,13 @@
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22" t="n">
-        <v>0.0000107</v>
+        <v>0.00000845</v>
       </c>
       <c r="W22" t="n">
-        <v>0.00000535</v>
+        <v>0.00000112</v>
       </c>
       <c r="X22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -4926,13 +5105,13 @@
       </c>
       <c r="AA22"/>
       <c r="AB22" t="n">
-        <v>0.00000267</v>
+        <v>0.00000516</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0000012</v>
+        <v>0.000000974</v>
       </c>
       <c r="AD22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4942,13 +5121,13 @@
       </c>
       <c r="AG22"/>
       <c r="AH22" t="n">
-        <v>-27.3921</v>
+        <v>-28.3647</v>
       </c>
       <c r="AI22" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK22" t="n">
         <v>400</v>
@@ -4963,7 +5142,7 @@
         <v>1.22</v>
       </c>
       <c r="AO22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP22" t="n">
         <v>0.68</v>
@@ -4979,7 +5158,7 @@
         <v>0.1</v>
       </c>
       <c r="AU22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV22" t="n">
         <v>1</v>
@@ -4988,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="AX22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY22" t="n">
         <v>1</v>
@@ -4997,7 +5176,7 @@
         <v>0.05</v>
       </c>
       <c r="BA22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -5006,7 +5185,7 @@
         <v>0.05</v>
       </c>
       <c r="BD22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE22" t="n">
         <v>0.2</v>
@@ -5015,7 +5194,7 @@
         <v>0.02</v>
       </c>
       <c r="BG22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH22" t="n">
         <v>0.013</v>
@@ -5024,25 +5203,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK22" s="1"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F23" t="n">
         <v>-45.527</v>
@@ -5051,31 +5230,31 @@
         <v>170.219</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>22.962</v>
+        <v>22.967</v>
       </c>
       <c r="I23" s="23"/>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
       <c r="L23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M23" t="s">
+        <v>217</v>
+      </c>
+      <c r="N23" t="s">
         <v>203</v>
       </c>
-      <c r="N23" t="s">
-        <v>204</v>
-      </c>
       <c r="O23" t="s">
+        <v>218</v>
+      </c>
+      <c r="P23" t="n">
+        <v>684375000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>126445887.6</v>
+      </c>
+      <c r="R23" t="s">
         <v>205</v>
-      </c>
-      <c r="P23" t="n">
-        <v>153333333.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>22771001.7</v>
-      </c>
-      <c r="R23" t="s">
-        <v>206</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5083,13 +5262,13 @@
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23" t="n">
-        <v>0.00000897</v>
+        <v>0.0000055</v>
       </c>
       <c r="W23" t="n">
-        <v>0.00000102</v>
+        <v>0.000000957</v>
       </c>
       <c r="X23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -5099,13 +5278,13 @@
       </c>
       <c r="AA23"/>
       <c r="AB23" t="n">
-        <v>0.00000453</v>
+        <v>0.00000118</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.000000742</v>
+        <v>0.000000327</v>
       </c>
       <c r="AD23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -5115,13 +5294,13 @@
       </c>
       <c r="AG23"/>
       <c r="AH23" t="n">
-        <v>-28.4748</v>
+        <v>-28.6689</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.293647</v>
+        <v>0.4</v>
       </c>
       <c r="AJ23" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK23" t="n">
         <v>400</v>
@@ -5136,7 +5315,7 @@
         <v>1.22</v>
       </c>
       <c r="AO23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP23" t="n">
         <v>0.68</v>
@@ -5152,7 +5331,7 @@
         <v>0.1</v>
       </c>
       <c r="AU23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV23" t="n">
         <v>1</v>
@@ -5161,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="AX23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
@@ -5170,7 +5349,7 @@
         <v>0.05</v>
       </c>
       <c r="BA23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB23" t="n">
         <v>1</v>
@@ -5179,7 +5358,7 @@
         <v>0.05</v>
       </c>
       <c r="BD23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE23" t="n">
         <v>0.2</v>
@@ -5188,7 +5367,7 @@
         <v>0.02</v>
       </c>
       <c r="BG23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH23" t="n">
         <v>0.013</v>
@@ -5197,25 +5376,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ23" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F24" t="n">
         <v>-45.527</v>
@@ -5224,31 +5403,31 @@
         <v>170.219</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>22.962</v>
+        <v>22.968</v>
       </c>
       <c r="I24" s="23"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" t="s">
+        <v>201</v>
+      </c>
+      <c r="M24" t="s">
         <v>202</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>203</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>204</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="n">
+        <v>255555555.6</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>36004114.99</v>
+      </c>
+      <c r="R24" t="s">
         <v>205</v>
-      </c>
-      <c r="P24" t="n">
-        <v>206666666.7</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>37350525.14</v>
-      </c>
-      <c r="R24" t="s">
-        <v>206</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5256,13 +5435,13 @@
       <c r="T24"/>
       <c r="U24"/>
       <c r="V24" t="n">
-        <v>0.00000845</v>
+        <v>0.0000146</v>
       </c>
       <c r="W24" t="n">
-        <v>0.00000112</v>
+        <v>0.00000567</v>
       </c>
       <c r="X24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -5272,13 +5451,13 @@
       </c>
       <c r="AA24"/>
       <c r="AB24" t="n">
-        <v>0.00000516</v>
+        <v>0.000003</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.000000974</v>
+        <v>0.00000153</v>
       </c>
       <c r="AD24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -5288,13 +5467,13 @@
       </c>
       <c r="AG24"/>
       <c r="AH24" t="n">
-        <v>-28.3647</v>
+        <v>-27.5724</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.4</v>
+        <v>0.372794</v>
       </c>
       <c r="AJ24" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK24" t="n">
         <v>400</v>
@@ -5309,7 +5488,7 @@
         <v>1.22</v>
       </c>
       <c r="AO24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP24" t="n">
         <v>0.68</v>
@@ -5325,7 +5504,7 @@
         <v>0.1</v>
       </c>
       <c r="AU24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -5334,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="AX24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY24" t="n">
         <v>1</v>
@@ -5343,7 +5522,7 @@
         <v>0.05</v>
       </c>
       <c r="BA24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB24" t="n">
         <v>1</v>
@@ -5352,7 +5531,7 @@
         <v>0.05</v>
       </c>
       <c r="BD24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE24" t="n">
         <v>0.2</v>
@@ -5361,7 +5540,7 @@
         <v>0.02</v>
       </c>
       <c r="BG24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH24" t="n">
         <v>0.013</v>
@@ -5370,25 +5549,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F25" t="n">
         <v>-45.527</v>
@@ -5397,31 +5576,31 @@
         <v>170.219</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>22.967</v>
+        <v>22.968</v>
       </c>
       <c r="I25" s="23"/>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M25" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="N25" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="O25" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P25" t="n">
-        <v>684375000</v>
+        <v>214930555.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>126445887.6</v>
+        <v>26958401.31</v>
       </c>
       <c r="R25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5429,13 +5608,13 @@
       <c r="T25"/>
       <c r="U25"/>
       <c r="V25" t="n">
-        <v>0.0000055</v>
+        <v>0.00001075</v>
       </c>
       <c r="W25" t="n">
-        <v>0.000000957</v>
+        <v>0.0000038</v>
       </c>
       <c r="X25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -5445,13 +5624,13 @@
       </c>
       <c r="AA25"/>
       <c r="AB25" t="n">
-        <v>0.00000118</v>
+        <v>0.00000175</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.000000327</v>
+        <v>0.000000504</v>
       </c>
       <c r="AD25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -5461,13 +5640,13 @@
       </c>
       <c r="AG25"/>
       <c r="AH25" t="n">
-        <v>-28.6689</v>
+        <v>-27.8479</v>
       </c>
       <c r="AI25" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK25" t="n">
         <v>400</v>
@@ -5476,13 +5655,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM25" t="n">
-        <v>6.86</v>
+        <v>7.51</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AO25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP25" t="n">
         <v>0.68</v>
@@ -5498,7 +5677,7 @@
         <v>0.1</v>
       </c>
       <c r="AU25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV25" t="n">
         <v>1</v>
@@ -5507,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="AX25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -5516,7 +5695,7 @@
         <v>0.05</v>
       </c>
       <c r="BA25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB25" t="n">
         <v>1</v>
@@ -5525,7 +5704,7 @@
         <v>0.05</v>
       </c>
       <c r="BD25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE25" t="n">
         <v>0.2</v>
@@ -5534,7 +5713,7 @@
         <v>0.02</v>
       </c>
       <c r="BG25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH25" t="n">
         <v>0.013</v>
@@ -5543,25 +5722,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK25" s="1"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C26" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F26" t="n">
         <v>-45.527</v>
@@ -5576,25 +5755,23 @@
       <c r="J26" s="23"/>
       <c r="K26" s="23"/>
       <c r="L26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M26" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="N26" t="s">
-        <v>204</v>
-      </c>
-      <c r="O26" t="s">
+        <v>212</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>47777260.98</v>
+      </c>
+      <c r="R26" t="s">
         <v>205</v>
-      </c>
-      <c r="P26" t="n">
-        <v>255555555.6</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>36004114.99</v>
-      </c>
-      <c r="R26" t="s">
-        <v>206</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5602,13 +5779,13 @@
       <c r="T26"/>
       <c r="U26"/>
       <c r="V26" t="n">
-        <v>0.0000146</v>
+        <v>0.00000975</v>
       </c>
       <c r="W26" t="n">
-        <v>0.00000567</v>
+        <v>0.00000408</v>
       </c>
       <c r="X26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -5618,13 +5795,13 @@
       </c>
       <c r="AA26"/>
       <c r="AB26" t="n">
-        <v>0.000003</v>
+        <v>0.0000025</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.00000153</v>
+        <v>0.00000126</v>
       </c>
       <c r="AD26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -5634,13 +5811,13 @@
       </c>
       <c r="AG26"/>
       <c r="AH26" t="n">
-        <v>-27.5724</v>
+        <v>-28.8986</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.372794</v>
+        <v>0.4</v>
       </c>
       <c r="AJ26" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK26" t="n">
         <v>400</v>
@@ -5649,13 +5826,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM26" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="AO26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP26" t="n">
         <v>0.68</v>
@@ -5671,7 +5848,7 @@
         <v>0.1</v>
       </c>
       <c r="AU26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV26" t="n">
         <v>1</v>
@@ -5680,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="AX26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
@@ -5689,7 +5866,7 @@
         <v>0.05</v>
       </c>
       <c r="BA26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5698,7 +5875,7 @@
         <v>0.05</v>
       </c>
       <c r="BD26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE26" t="n">
         <v>0.2</v>
@@ -5707,7 +5884,7 @@
         <v>0.02</v>
       </c>
       <c r="BG26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH26" t="n">
         <v>0.013</v>
@@ -5716,25 +5893,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK26" s="1"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D27" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F27" t="n">
         <v>-45.527</v>
@@ -5743,31 +5920,31 @@
         <v>170.219</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>22.968</v>
+        <v>22.97</v>
       </c>
       <c r="I27" s="23"/>
       <c r="J27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" t="s">
+        <v>201</v>
+      </c>
+      <c r="M27" t="s">
         <v>202</v>
       </c>
-      <c r="M27" t="s">
-        <v>236</v>
-      </c>
       <c r="N27" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="O27" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="P27" t="n">
-        <v>214930555.6</v>
+        <v>185185185.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>26958401.31</v>
+        <v>45902024.84</v>
       </c>
       <c r="R27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5775,13 +5952,13 @@
       <c r="T27"/>
       <c r="U27"/>
       <c r="V27" t="n">
-        <v>0.00001075</v>
+        <v>0.00000879</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0000038</v>
+        <v>0.000000828</v>
       </c>
       <c r="X27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -5791,13 +5968,13 @@
       </c>
       <c r="AA27"/>
       <c r="AB27" t="n">
-        <v>0.00000175</v>
+        <v>0.00000525</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.000000504</v>
+        <v>0.000000647</v>
       </c>
       <c r="AD27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -5807,13 +5984,13 @@
       </c>
       <c r="AG27"/>
       <c r="AH27" t="n">
-        <v>-27.8479</v>
+        <v>-26.8432</v>
       </c>
       <c r="AI27" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK27" t="n">
         <v>400</v>
@@ -5822,13 +5999,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM27" t="n">
-        <v>7.51</v>
+        <v>6.86</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AO27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP27" t="n">
         <v>0.68</v>
@@ -5844,7 +6021,7 @@
         <v>0.1</v>
       </c>
       <c r="AU27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV27" t="n">
         <v>1</v>
@@ -5853,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="AX27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY27" t="n">
         <v>1</v>
@@ -5862,7 +6039,7 @@
         <v>0.05</v>
       </c>
       <c r="BA27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB27" t="n">
         <v>1</v>
@@ -5871,7 +6048,7 @@
         <v>0.05</v>
       </c>
       <c r="BD27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE27" t="n">
         <v>0.2</v>
@@ -5880,7 +6057,7 @@
         <v>0.02</v>
       </c>
       <c r="BG27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH27" t="n">
         <v>0.013</v>
@@ -5889,25 +6066,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F28" t="n">
         <v>-45.527</v>
@@ -5916,29 +6093,31 @@
         <v>170.219</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>22.968</v>
+        <v>22.97</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s">
-        <v>213</v>
-      </c>
-      <c r="O28"/>
+        <v>203</v>
+      </c>
+      <c r="O28" t="s">
+        <v>218</v>
+      </c>
       <c r="P28" t="n">
-        <v>380000000</v>
+        <v>751851851.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>47777260.98</v>
+        <v>111296142.2</v>
       </c>
       <c r="R28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5946,13 +6125,13 @@
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28" t="n">
-        <v>0.00000975</v>
+        <v>0.00000551</v>
       </c>
       <c r="W28" t="n">
-        <v>0.00000408</v>
+        <v>0.000000944</v>
       </c>
       <c r="X28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -5962,13 +6141,13 @@
       </c>
       <c r="AA28"/>
       <c r="AB28" t="n">
-        <v>0.0000025</v>
+        <v>0.00000348</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.00000126</v>
+        <v>0.000000552</v>
       </c>
       <c r="AD28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -5978,13 +6157,13 @@
       </c>
       <c r="AG28"/>
       <c r="AH28" t="n">
-        <v>-28.8986</v>
+        <v>-28.855</v>
       </c>
       <c r="AI28" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK28" t="n">
         <v>400</v>
@@ -5993,13 +6172,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM28" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP28" t="n">
         <v>0.68</v>
@@ -6015,7 +6194,7 @@
         <v>0.1</v>
       </c>
       <c r="AU28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -6024,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="AX28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY28" t="n">
         <v>1</v>
@@ -6033,7 +6212,7 @@
         <v>0.05</v>
       </c>
       <c r="BA28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB28" t="n">
         <v>1</v>
@@ -6042,7 +6221,7 @@
         <v>0.05</v>
       </c>
       <c r="BD28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE28" t="n">
         <v>0.2</v>
@@ -6051,7 +6230,7 @@
         <v>0.02</v>
       </c>
       <c r="BG28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH28" t="n">
         <v>0.013</v>
@@ -6060,25 +6239,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK28" s="1"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F29" t="n">
         <v>-45.527</v>
@@ -6087,31 +6266,31 @@
         <v>170.219</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>22.97</v>
+        <v>22.971</v>
       </c>
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" t="s">
         <v>202</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>203</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>204</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="n">
+        <v>320000000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>43319085.98</v>
+      </c>
+      <c r="R29" t="s">
         <v>205</v>
-      </c>
-      <c r="P29" t="n">
-        <v>185185185.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>45902024.84</v>
-      </c>
-      <c r="R29" t="s">
-        <v>206</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6119,13 +6298,13 @@
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29" t="n">
-        <v>0.00000879</v>
+        <v>0.00000768</v>
       </c>
       <c r="W29" t="n">
-        <v>0.000000828</v>
+        <v>0.00000104</v>
       </c>
       <c r="X29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -6135,13 +6314,13 @@
       </c>
       <c r="AA29"/>
       <c r="AB29" t="n">
-        <v>0.00000525</v>
+        <v>0.00000424</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.000000647</v>
+        <v>0.000000799</v>
       </c>
       <c r="AD29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -6151,13 +6330,13 @@
       </c>
       <c r="AG29"/>
       <c r="AH29" t="n">
-        <v>-26.8432</v>
+        <v>-27.5552</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.4</v>
+        <v>0.137121</v>
       </c>
       <c r="AJ29" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK29" t="n">
         <v>400</v>
@@ -6172,7 +6351,7 @@
         <v>1.22</v>
       </c>
       <c r="AO29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP29" t="n">
         <v>0.68</v>
@@ -6188,7 +6367,7 @@
         <v>0.1</v>
       </c>
       <c r="AU29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV29" t="n">
         <v>1</v>
@@ -6197,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="AX29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY29" t="n">
         <v>1</v>
@@ -6206,7 +6385,7 @@
         <v>0.05</v>
       </c>
       <c r="BA29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB29" t="n">
         <v>1</v>
@@ -6215,7 +6394,7 @@
         <v>0.05</v>
       </c>
       <c r="BD29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE29" t="n">
         <v>0.2</v>
@@ -6224,7 +6403,7 @@
         <v>0.02</v>
       </c>
       <c r="BG29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH29" t="n">
         <v>0.013</v>
@@ -6233,25 +6412,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK29" s="1"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F30" t="n">
         <v>-45.527</v>
@@ -6260,31 +6439,31 @@
         <v>170.219</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>22.97</v>
+        <v>22.971</v>
       </c>
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
       <c r="K30" s="23"/>
       <c r="L30" t="s">
+        <v>201</v>
+      </c>
+      <c r="M30" t="s">
         <v>202</v>
       </c>
-      <c r="M30" t="s">
-        <v>218</v>
-      </c>
       <c r="N30" t="s">
+        <v>203</v>
+      </c>
+      <c r="O30" t="s">
         <v>204</v>
       </c>
-      <c r="O30" t="s">
-        <v>219</v>
-      </c>
       <c r="P30" t="n">
-        <v>751851851.9</v>
+        <v>200000000</v>
       </c>
       <c r="Q30" t="n">
-        <v>111296142.2</v>
+        <v>47140452.08</v>
       </c>
       <c r="R30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6292,13 +6471,13 @@
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30" t="n">
-        <v>0.00000551</v>
+        <v>0.00001025</v>
       </c>
       <c r="W30" t="n">
-        <v>0.000000944</v>
+        <v>0.00000163</v>
       </c>
       <c r="X30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -6308,13 +6487,13 @@
       </c>
       <c r="AA30"/>
       <c r="AB30" t="n">
-        <v>0.00000348</v>
+        <v>0.00000175</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.000000552</v>
+        <v>0.000000557</v>
       </c>
       <c r="AD30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -6324,13 +6503,13 @@
       </c>
       <c r="AG30"/>
       <c r="AH30" t="n">
-        <v>-28.855</v>
+        <v>-26.0839</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.4</v>
+        <v>0.492739</v>
       </c>
       <c r="AJ30" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK30" t="n">
         <v>400</v>
@@ -6345,7 +6524,7 @@
         <v>1.22</v>
       </c>
       <c r="AO30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP30" t="n">
         <v>0.68</v>
@@ -6361,7 +6540,7 @@
         <v>0.1</v>
       </c>
       <c r="AU30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV30" t="n">
         <v>1</v>
@@ -6370,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="AX30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY30" t="n">
         <v>1</v>
@@ -6379,7 +6558,7 @@
         <v>0.05</v>
       </c>
       <c r="BA30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB30" t="n">
         <v>1</v>
@@ -6388,7 +6567,7 @@
         <v>0.05</v>
       </c>
       <c r="BD30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE30" t="n">
         <v>0.2</v>
@@ -6397,7 +6576,7 @@
         <v>0.02</v>
       </c>
       <c r="BG30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH30" t="n">
         <v>0.013</v>
@@ -6406,25 +6585,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK30" s="1"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F31" t="n">
         <v>-45.527</v>
@@ -6439,25 +6618,25 @@
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" t="s">
         <v>202</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>203</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>204</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="n">
+        <v>279629629.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>126377187.1</v>
+      </c>
+      <c r="R31" t="s">
         <v>205</v>
-      </c>
-      <c r="P31" t="n">
-        <v>320000000</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>43319085.98</v>
-      </c>
-      <c r="R31" t="s">
-        <v>206</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6465,13 +6644,13 @@
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31" t="n">
-        <v>0.00000768</v>
+        <v>0.0000293</v>
       </c>
       <c r="W31" t="n">
-        <v>0.00000104</v>
+        <v>0.0000205</v>
       </c>
       <c r="X31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -6481,13 +6660,13 @@
       </c>
       <c r="AA31"/>
       <c r="AB31" t="n">
-        <v>0.00000424</v>
+        <v>0.00000213</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.000000799</v>
+        <v>0.00000181</v>
       </c>
       <c r="AD31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -6497,13 +6676,13 @@
       </c>
       <c r="AG31"/>
       <c r="AH31" t="n">
-        <v>-27.5552</v>
+        <v>-27.3374</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.137121</v>
+        <v>0.4</v>
       </c>
       <c r="AJ31" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK31" t="n">
         <v>400</v>
@@ -6518,7 +6697,7 @@
         <v>1.22</v>
       </c>
       <c r="AO31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP31" t="n">
         <v>0.68</v>
@@ -6534,7 +6713,7 @@
         <v>0.1</v>
       </c>
       <c r="AU31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV31" t="n">
         <v>1</v>
@@ -6543,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="AX31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY31" t="n">
         <v>1</v>
@@ -6552,7 +6731,7 @@
         <v>0.05</v>
       </c>
       <c r="BA31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB31" t="n">
         <v>1</v>
@@ -6561,7 +6740,7 @@
         <v>0.05</v>
       </c>
       <c r="BD31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE31" t="n">
         <v>0.2</v>
@@ -6570,7 +6749,7 @@
         <v>0.02</v>
       </c>
       <c r="BG31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH31" t="n">
         <v>0.013</v>
@@ -6579,25 +6758,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK31" s="1"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F32" t="n">
         <v>-45.527</v>
@@ -6612,25 +6791,25 @@
       <c r="J32" s="23"/>
       <c r="K32" s="23"/>
       <c r="L32" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M32" t="s">
+        <v>217</v>
+      </c>
+      <c r="N32" t="s">
         <v>203</v>
       </c>
-      <c r="N32" t="s">
-        <v>204</v>
-      </c>
       <c r="O32" t="s">
+        <v>218</v>
+      </c>
+      <c r="P32" t="n">
+        <v>591111111.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>42600643.36</v>
+      </c>
+      <c r="R32" t="s">
         <v>205</v>
-      </c>
-      <c r="P32" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>47140452.08</v>
-      </c>
-      <c r="R32" t="s">
-        <v>206</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6638,13 +6817,13 @@
       <c r="T32"/>
       <c r="U32"/>
       <c r="V32" t="n">
-        <v>0.00001025</v>
+        <v>0.000007</v>
       </c>
       <c r="W32" t="n">
-        <v>0.00000163</v>
+        <v>0.00000302</v>
       </c>
       <c r="X32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -6654,13 +6833,13 @@
       </c>
       <c r="AA32"/>
       <c r="AB32" t="n">
-        <v>0.00000175</v>
+        <v>0.0000016</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.000000557</v>
+        <v>0.000000885</v>
       </c>
       <c r="AD32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -6670,13 +6849,13 @@
       </c>
       <c r="AG32"/>
       <c r="AH32" t="n">
-        <v>-26.0839</v>
+        <v>-29.9184</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.492739</v>
+        <v>0.4</v>
       </c>
       <c r="AJ32" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK32" t="n">
         <v>400</v>
@@ -6691,7 +6870,7 @@
         <v>1.22</v>
       </c>
       <c r="AO32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP32" t="n">
         <v>0.68</v>
@@ -6707,7 +6886,7 @@
         <v>0.1</v>
       </c>
       <c r="AU32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV32" t="n">
         <v>1</v>
@@ -6716,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="AX32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY32" t="n">
         <v>1</v>
@@ -6725,7 +6904,7 @@
         <v>0.05</v>
       </c>
       <c r="BA32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB32" t="n">
         <v>1</v>
@@ -6734,7 +6913,7 @@
         <v>0.05</v>
       </c>
       <c r="BD32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE32" t="n">
         <v>0.2</v>
@@ -6743,7 +6922,7 @@
         <v>0.02</v>
       </c>
       <c r="BG32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH32" t="n">
         <v>0.013</v>
@@ -6752,25 +6931,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK32" s="1"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F33" t="n">
         <v>-45.527</v>
@@ -6779,31 +6958,31 @@
         <v>170.219</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>22.971</v>
+        <v>22.972</v>
       </c>
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
       <c r="K33" s="23"/>
       <c r="L33" t="s">
+        <v>201</v>
+      </c>
+      <c r="M33" t="s">
         <v>202</v>
       </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
         <v>203</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>204</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="n">
+        <v>303703703.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>55924699.52</v>
+      </c>
+      <c r="R33" t="s">
         <v>205</v>
-      </c>
-      <c r="P33" t="n">
-        <v>279629629.6</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>126377187.1</v>
-      </c>
-      <c r="R33" t="s">
-        <v>206</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6811,13 +6990,13 @@
       <c r="T33"/>
       <c r="U33"/>
       <c r="V33" t="n">
-        <v>0.0000293</v>
+        <v>0.00000988</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0000205</v>
+        <v>0.000000931</v>
       </c>
       <c r="X33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -6827,13 +7006,13 @@
       </c>
       <c r="AA33"/>
       <c r="AB33" t="n">
-        <v>0.00000213</v>
+        <v>0.000006432</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.00000181</v>
+        <v>0.000000656</v>
       </c>
       <c r="AD33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -6843,13 +7022,13 @@
       </c>
       <c r="AG33"/>
       <c r="AH33" t="n">
-        <v>-27.3374</v>
+        <v>-27.3791</v>
       </c>
       <c r="AI33" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK33" t="n">
         <v>400</v>
@@ -6864,7 +7043,7 @@
         <v>1.22</v>
       </c>
       <c r="AO33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP33" t="n">
         <v>0.68</v>
@@ -6880,7 +7059,7 @@
         <v>0.1</v>
       </c>
       <c r="AU33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
@@ -6889,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="AX33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY33" t="n">
         <v>1</v>
@@ -6898,7 +7077,7 @@
         <v>0.05</v>
       </c>
       <c r="BA33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB33" t="n">
         <v>1</v>
@@ -6907,7 +7086,7 @@
         <v>0.05</v>
       </c>
       <c r="BD33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE33" t="n">
         <v>0.2</v>
@@ -6916,7 +7095,7 @@
         <v>0.02</v>
       </c>
       <c r="BG33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH33" t="n">
         <v>0.013</v>
@@ -6925,25 +7104,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK33" s="1"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F34" t="n">
         <v>-45.527</v>
@@ -6952,31 +7131,31 @@
         <v>170.219</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>22.971</v>
+        <v>22.972</v>
       </c>
       <c r="I34" s="23"/>
       <c r="J34" s="23"/>
       <c r="K34" s="23"/>
       <c r="L34" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s">
+        <v>217</v>
+      </c>
+      <c r="N34" t="s">
+        <v>203</v>
+      </c>
+      <c r="O34" t="s">
         <v>218</v>
       </c>
-      <c r="N34" t="s">
-        <v>204</v>
-      </c>
-      <c r="O34" t="s">
-        <v>219</v>
-      </c>
       <c r="P34" t="n">
-        <v>591111111.1</v>
+        <v>638888888.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>42600643.36</v>
+        <v>39020939.83</v>
       </c>
       <c r="R34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -6984,13 +7163,13 @@
       <c r="T34"/>
       <c r="U34"/>
       <c r="V34" t="n">
-        <v>0.000007</v>
+        <v>0.00000525</v>
       </c>
       <c r="W34" t="n">
-        <v>0.00000302</v>
+        <v>0.00000101</v>
       </c>
       <c r="X34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -7000,13 +7179,13 @@
       </c>
       <c r="AA34"/>
       <c r="AB34" t="n">
-        <v>0.0000016</v>
+        <v>0.00000125</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.000000885</v>
+        <v>0.000000479</v>
       </c>
       <c r="AD34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -7016,13 +7195,13 @@
       </c>
       <c r="AG34"/>
       <c r="AH34" t="n">
-        <v>-29.9184</v>
+        <v>-28.7787</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.4</v>
+        <v>0.756865</v>
       </c>
       <c r="AJ34" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK34" t="n">
         <v>400</v>
@@ -7037,7 +7216,7 @@
         <v>1.22</v>
       </c>
       <c r="AO34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP34" t="n">
         <v>0.68</v>
@@ -7053,7 +7232,7 @@
         <v>0.1</v>
       </c>
       <c r="AU34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
@@ -7062,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="AX34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY34" t="n">
         <v>1</v>
@@ -7071,7 +7250,7 @@
         <v>0.05</v>
       </c>
       <c r="BA34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB34" t="n">
         <v>1</v>
@@ -7080,7 +7259,7 @@
         <v>0.05</v>
       </c>
       <c r="BD34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE34" t="n">
         <v>0.2</v>
@@ -7089,7 +7268,7 @@
         <v>0.02</v>
       </c>
       <c r="BG34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH34" t="n">
         <v>0.013</v>
@@ -7098,25 +7277,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK34" s="1"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F35" t="n">
         <v>-45.527</v>
@@ -7131,25 +7310,25 @@
       <c r="J35" s="23"/>
       <c r="K35" s="23"/>
       <c r="L35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M35" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="O35" t="s">
+        <v>237</v>
+      </c>
+      <c r="P35" t="n">
+        <v>472222222.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>98757715.75</v>
+      </c>
+      <c r="R35" t="s">
         <v>205</v>
-      </c>
-      <c r="P35" t="n">
-        <v>303703703.7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>55924699.52</v>
-      </c>
-      <c r="R35" t="s">
-        <v>206</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7157,13 +7336,13 @@
       <c r="T35"/>
       <c r="U35"/>
       <c r="V35" t="n">
-        <v>0.00000988</v>
+        <v>0.000007272</v>
       </c>
       <c r="W35" t="n">
-        <v>0.000000931</v>
+        <v>0.00000173</v>
       </c>
       <c r="X35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -7173,13 +7352,13 @@
       </c>
       <c r="AA35"/>
       <c r="AB35" t="n">
-        <v>0.000006432</v>
+        <v>0.000002749</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.000000656</v>
+        <v>0.000000716</v>
       </c>
       <c r="AD35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -7189,13 +7368,13 @@
       </c>
       <c r="AG35"/>
       <c r="AH35" t="n">
-        <v>-27.3791</v>
+        <v>-27.5095</v>
       </c>
       <c r="AI35" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK35" t="n">
         <v>400</v>
@@ -7204,13 +7383,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM35" t="n">
-        <v>6.86</v>
+        <v>7.51</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AO35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP35" t="n">
         <v>0.68</v>
@@ -7226,7 +7405,7 @@
         <v>0.1</v>
       </c>
       <c r="AU35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV35" t="n">
         <v>1</v>
@@ -7235,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="AX35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY35" t="n">
         <v>1</v>
@@ -7244,7 +7423,7 @@
         <v>0.05</v>
       </c>
       <c r="BA35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB35" t="n">
         <v>1</v>
@@ -7253,7 +7432,7 @@
         <v>0.05</v>
       </c>
       <c r="BD35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE35" t="n">
         <v>0.2</v>
@@ -7262,7 +7441,7 @@
         <v>0.02</v>
       </c>
       <c r="BG35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH35" t="n">
         <v>0.013</v>
@@ -7271,23 +7450,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK35" s="1"/>
     </row>
     <row r="36">
-      <c r="A36"/>
+      <c r="A36" t="s">
+        <v>248</v>
+      </c>
       <c r="B36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F36" t="n">
         <v>-45.527</v>
@@ -7296,85 +7477,171 @@
         <v>170.219</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>22.988</v>
+        <v>22.973</v>
       </c>
       <c r="I36" s="23"/>
-      <c r="J36" s="23" t="n">
-        <v>22.973</v>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>22.993</v>
-      </c>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
       <c r="L36" t="s">
-        <v>200</v>
-      </c>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-      <c r="S36"/>
+        <v>201</v>
+      </c>
+      <c r="M36" t="s">
+        <v>217</v>
+      </c>
+      <c r="N36" t="s">
+        <v>203</v>
+      </c>
+      <c r="O36" t="s">
+        <v>218</v>
+      </c>
+      <c r="P36" t="n">
+        <v>415555555.6</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>64117946.87</v>
+      </c>
+      <c r="R36" t="s">
+        <v>205</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
       <c r="T36"/>
       <c r="U36"/>
-      <c r="V36"/>
-      <c r="W36"/>
-      <c r="X36"/>
-      <c r="Y36"/>
-      <c r="Z36"/>
+      <c r="V36" t="n">
+        <v>0.000006028</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.000000969</v>
+      </c>
+      <c r="X36" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
       <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36"/>
-      <c r="AD36"/>
-      <c r="AE36"/>
-      <c r="AF36"/>
+      <c r="AB36" t="n">
+        <v>0.000005568</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.00000107</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
       <c r="AG36"/>
-      <c r="AH36"/>
-      <c r="AI36"/>
-      <c r="AJ36"/>
-      <c r="AK36"/>
-      <c r="AL36"/>
-      <c r="AM36"/>
-      <c r="AN36"/>
-      <c r="AO36"/>
-      <c r="AP36"/>
-      <c r="AQ36"/>
+      <c r="AH36" t="n">
+        <v>-28.3906</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.294724</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>400</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.000714286</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>208</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AR36"/>
-      <c r="AS36"/>
-      <c r="AT36"/>
-      <c r="AU36"/>
-      <c r="AV36"/>
-      <c r="AW36"/>
-      <c r="AX36"/>
-      <c r="AY36"/>
-      <c r="AZ36"/>
-      <c r="BA36"/>
-      <c r="BB36"/>
-      <c r="BC36"/>
-      <c r="BD36"/>
-      <c r="BE36"/>
-      <c r="BF36"/>
-      <c r="BG36"/>
-      <c r="BH36"/>
-      <c r="BI36"/>
-      <c r="BJ36"/>
+      <c r="AS36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU36" t="s">
+        <v>209</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA36" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD36" t="s">
+        <v>209</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BG36" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BJ36" t="s">
+        <v>209</v>
+      </c>
       <c r="BK36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F37" t="n">
         <v>-45.527</v>
@@ -7383,31 +7650,31 @@
         <v>170.219</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>22.972</v>
+        <v>22.986</v>
       </c>
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
       <c r="K37" s="23"/>
       <c r="L37" t="s">
+        <v>201</v>
+      </c>
+      <c r="M37" t="s">
         <v>202</v>
       </c>
-      <c r="M37" t="s">
-        <v>218</v>
-      </c>
       <c r="N37" t="s">
+        <v>203</v>
+      </c>
+      <c r="O37" t="s">
         <v>204</v>
       </c>
-      <c r="O37" t="s">
-        <v>219</v>
-      </c>
       <c r="P37" t="n">
-        <v>638888888.9</v>
+        <v>204444444.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>39020939.83</v>
+        <v>57520796.02</v>
       </c>
       <c r="R37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7415,13 +7682,13 @@
       <c r="T37"/>
       <c r="U37"/>
       <c r="V37" t="n">
-        <v>0.00000525</v>
+        <v>0.0000084</v>
       </c>
       <c r="W37" t="n">
-        <v>0.00000101</v>
+        <v>0.00000102</v>
       </c>
       <c r="X37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -7431,13 +7698,13 @@
       </c>
       <c r="AA37"/>
       <c r="AB37" t="n">
-        <v>0.00000125</v>
+        <v>0.00000533</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.000000479</v>
+        <v>0.000000781</v>
       </c>
       <c r="AD37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -7447,13 +7714,13 @@
       </c>
       <c r="AG37"/>
       <c r="AH37" t="n">
-        <v>-28.7787</v>
+        <v>-29.6962</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.756865</v>
+        <v>0.4</v>
       </c>
       <c r="AJ37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK37" t="n">
         <v>400</v>
@@ -7468,7 +7735,7 @@
         <v>1.22</v>
       </c>
       <c r="AO37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP37" t="n">
         <v>0.68</v>
@@ -7484,7 +7751,7 @@
         <v>0.1</v>
       </c>
       <c r="AU37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV37" t="n">
         <v>1</v>
@@ -7493,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="AX37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY37" t="n">
         <v>1</v>
@@ -7502,7 +7769,7 @@
         <v>0.05</v>
       </c>
       <c r="BA37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB37" t="n">
         <v>1</v>
@@ -7511,7 +7778,7 @@
         <v>0.05</v>
       </c>
       <c r="BD37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE37" t="n">
         <v>0.2</v>
@@ -7520,7 +7787,7 @@
         <v>0.02</v>
       </c>
       <c r="BG37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH37" t="n">
         <v>0.013</v>
@@ -7529,25 +7796,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D38" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F38" t="n">
         <v>-45.527</v>
@@ -7556,31 +7823,29 @@
         <v>170.219</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>22.972</v>
+        <v>22.987</v>
       </c>
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
       <c r="K38" s="23"/>
       <c r="L38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M38" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="N38" t="s">
-        <v>237</v>
-      </c>
-      <c r="O38" t="s">
-        <v>238</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O38"/>
       <c r="P38" t="n">
-        <v>472222222.2</v>
+        <v>577777777.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>98757715.75</v>
+        <v>59317101.4</v>
       </c>
       <c r="R38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7588,13 +7853,13 @@
       <c r="T38"/>
       <c r="U38"/>
       <c r="V38" t="n">
-        <v>0.000007272</v>
+        <v>0.0000068</v>
       </c>
       <c r="W38" t="n">
-        <v>0.00000173</v>
+        <v>0.00000328</v>
       </c>
       <c r="X38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -7604,13 +7869,13 @@
       </c>
       <c r="AA38"/>
       <c r="AB38" t="n">
-        <v>0.000002749</v>
+        <v>0.0000014</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.000000716</v>
+        <v>0.000000741</v>
       </c>
       <c r="AD38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -7620,13 +7885,13 @@
       </c>
       <c r="AG38"/>
       <c r="AH38" t="n">
-        <v>-27.5095</v>
+        <v>-28.7137</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.4</v>
+        <v>0.593574</v>
       </c>
       <c r="AJ38" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK38" t="n">
         <v>400</v>
@@ -7635,13 +7900,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM38" t="n">
-        <v>7.51</v>
+        <v>7.31</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AO38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP38" t="n">
         <v>0.68</v>
@@ -7657,7 +7922,7 @@
         <v>0.1</v>
       </c>
       <c r="AU38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV38" t="n">
         <v>1</v>
@@ -7666,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="AX38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY38" t="n">
         <v>1</v>
@@ -7675,7 +7940,7 @@
         <v>0.05</v>
       </c>
       <c r="BA38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB38" t="n">
         <v>1</v>
@@ -7684,7 +7949,7 @@
         <v>0.05</v>
       </c>
       <c r="BD38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE38" t="n">
         <v>0.2</v>
@@ -7693,7 +7958,7 @@
         <v>0.02</v>
       </c>
       <c r="BG38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH38" t="n">
         <v>0.013</v>
@@ -7702,25 +7967,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK38" s="1"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F39" t="n">
         <v>-45.527</v>
@@ -7729,31 +7994,31 @@
         <v>170.219</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>22.973</v>
+        <v>22.987</v>
       </c>
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
       <c r="K39" s="23"/>
       <c r="L39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M39" t="s">
+        <v>217</v>
+      </c>
+      <c r="N39" t="s">
+        <v>203</v>
+      </c>
+      <c r="O39" t="s">
         <v>218</v>
       </c>
-      <c r="N39" t="s">
-        <v>204</v>
-      </c>
-      <c r="O39" t="s">
-        <v>219</v>
-      </c>
       <c r="P39" t="n">
-        <v>415555555.6</v>
+        <v>362222222.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>64117946.87</v>
+        <v>73114150.56</v>
       </c>
       <c r="R39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -7761,13 +8026,13 @@
       <c r="T39"/>
       <c r="U39"/>
       <c r="V39" t="n">
-        <v>0.000006028</v>
+        <v>0.0000082</v>
       </c>
       <c r="W39" t="n">
-        <v>0.000000969</v>
+        <v>0.00000295</v>
       </c>
       <c r="X39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -7777,13 +8042,13 @@
       </c>
       <c r="AA39"/>
       <c r="AB39" t="n">
-        <v>0.000005568</v>
+        <v>0.0000028</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.00000107</v>
+        <v>0.00000104</v>
       </c>
       <c r="AD39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -7793,13 +8058,13 @@
       </c>
       <c r="AG39"/>
       <c r="AH39" t="n">
-        <v>-28.3906</v>
+        <v>-28.2781</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.294724</v>
+        <v>0.4</v>
       </c>
       <c r="AJ39" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK39" t="n">
         <v>400</v>
@@ -7814,7 +8079,7 @@
         <v>1.22</v>
       </c>
       <c r="AO39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP39" t="n">
         <v>0.68</v>
@@ -7830,7 +8095,7 @@
         <v>0.1</v>
       </c>
       <c r="AU39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV39" t="n">
         <v>1</v>
@@ -7839,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="AX39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY39" t="n">
         <v>1</v>
@@ -7848,7 +8113,7 @@
         <v>0.05</v>
       </c>
       <c r="BA39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB39" t="n">
         <v>1</v>
@@ -7857,7 +8122,7 @@
         <v>0.05</v>
       </c>
       <c r="BD39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE39" t="n">
         <v>0.2</v>
@@ -7866,7 +8131,7 @@
         <v>0.02</v>
       </c>
       <c r="BG39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH39" t="n">
         <v>0.013</v>
@@ -7875,25 +8140,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK39" s="1"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F40" t="n">
         <v>-45.527</v>
@@ -7902,31 +8167,31 @@
         <v>170.219</v>
       </c>
       <c r="H40" s="23" t="n">
-        <v>22.986</v>
+        <v>22.992</v>
       </c>
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
       <c r="K40" s="23"/>
       <c r="L40" t="s">
+        <v>201</v>
+      </c>
+      <c r="M40" t="s">
         <v>202</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>203</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>204</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>39544734.27</v>
+      </c>
+      <c r="R40" t="s">
         <v>205</v>
-      </c>
-      <c r="P40" t="n">
-        <v>204444444.4</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>57520796.02</v>
-      </c>
-      <c r="R40" t="s">
-        <v>206</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -7934,13 +8199,13 @@
       <c r="T40"/>
       <c r="U40"/>
       <c r="V40" t="n">
-        <v>0.0000084</v>
+        <v>0.00000899</v>
       </c>
       <c r="W40" t="n">
-        <v>0.00000102</v>
+        <v>0.00000122</v>
       </c>
       <c r="X40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -7950,13 +8215,13 @@
       </c>
       <c r="AA40"/>
       <c r="AB40" t="n">
-        <v>0.00000533</v>
+        <v>0.00000517</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.000000781</v>
+        <v>0.00000078</v>
       </c>
       <c r="AD40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -7966,13 +8231,13 @@
       </c>
       <c r="AG40"/>
       <c r="AH40" t="n">
-        <v>-29.6962</v>
+        <v>-27.7324</v>
       </c>
       <c r="AI40" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK40" t="n">
         <v>400</v>
@@ -7987,7 +8252,7 @@
         <v>1.22</v>
       </c>
       <c r="AO40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP40" t="n">
         <v>0.68</v>
@@ -8003,7 +8268,7 @@
         <v>0.1</v>
       </c>
       <c r="AU40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV40" t="n">
         <v>1</v>
@@ -8012,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="AX40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY40" t="n">
         <v>1</v>
@@ -8021,7 +8286,7 @@
         <v>0.05</v>
       </c>
       <c r="BA40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB40" t="n">
         <v>1</v>
@@ -8030,7 +8295,7 @@
         <v>0.05</v>
       </c>
       <c r="BD40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE40" t="n">
         <v>0.2</v>
@@ -8039,7 +8304,7 @@
         <v>0.02</v>
       </c>
       <c r="BG40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH40" t="n">
         <v>0.013</v>
@@ -8048,25 +8313,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK40" s="1"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F41" t="n">
         <v>-45.527</v>
@@ -8075,29 +8340,31 @@
         <v>170.219</v>
       </c>
       <c r="H41" s="23" t="n">
-        <v>22.987</v>
+        <v>22.992</v>
       </c>
       <c r="I41" s="23"/>
       <c r="J41" s="23"/>
       <c r="K41" s="23"/>
       <c r="L41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M41" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N41" t="s">
-        <v>213</v>
-      </c>
-      <c r="O41"/>
+        <v>203</v>
+      </c>
+      <c r="O41" t="s">
+        <v>218</v>
+      </c>
       <c r="P41" t="n">
-        <v>577777777.8</v>
+        <v>406666666.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>59317101.4</v>
+        <v>32960882.16</v>
       </c>
       <c r="R41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8105,13 +8372,13 @@
       <c r="T41"/>
       <c r="U41"/>
       <c r="V41" t="n">
-        <v>0.0000068</v>
+        <v>0.00000725</v>
       </c>
       <c r="W41" t="n">
-        <v>0.00000328</v>
+        <v>0.00000101</v>
       </c>
       <c r="X41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -8121,13 +8388,13 @@
       </c>
       <c r="AA41"/>
       <c r="AB41" t="n">
-        <v>0.0000014</v>
+        <v>0.00000388</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.000000741</v>
+        <v>0.000000546</v>
       </c>
       <c r="AD41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -8137,13 +8404,13 @@
       </c>
       <c r="AG41"/>
       <c r="AH41" t="n">
-        <v>-28.7137</v>
+        <v>-30.1941</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.593574</v>
+        <v>0.024978</v>
       </c>
       <c r="AJ41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK41" t="n">
         <v>400</v>
@@ -8152,13 +8419,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM41" t="n">
-        <v>7.31</v>
+        <v>6.86</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP41" t="n">
         <v>0.68</v>
@@ -8174,7 +8441,7 @@
         <v>0.1</v>
       </c>
       <c r="AU41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV41" t="n">
         <v>1</v>
@@ -8183,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="AX41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY41" t="n">
         <v>1</v>
@@ -8192,7 +8459,7 @@
         <v>0.05</v>
       </c>
       <c r="BA41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB41" t="n">
         <v>1</v>
@@ -8201,7 +8468,7 @@
         <v>0.05</v>
       </c>
       <c r="BD41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE41" t="n">
         <v>0.2</v>
@@ -8210,7 +8477,7 @@
         <v>0.02</v>
       </c>
       <c r="BG41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH41" t="n">
         <v>0.013</v>
@@ -8219,25 +8486,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK41" s="1"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F42" t="n">
         <v>-45.527</v>
@@ -8246,31 +8513,31 @@
         <v>170.219</v>
       </c>
       <c r="H42" s="23" t="n">
-        <v>22.987</v>
+        <v>22.993</v>
       </c>
       <c r="I42" s="23"/>
       <c r="J42" s="23"/>
       <c r="K42" s="23"/>
       <c r="L42" t="s">
+        <v>201</v>
+      </c>
+      <c r="M42" t="s">
         <v>202</v>
       </c>
-      <c r="M42" t="s">
-        <v>218</v>
-      </c>
       <c r="N42" t="s">
+        <v>203</v>
+      </c>
+      <c r="O42" t="s">
         <v>204</v>
       </c>
-      <c r="O42" t="s">
-        <v>219</v>
-      </c>
       <c r="P42" t="n">
-        <v>362222222.2</v>
+        <v>133333333.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>73114150.56</v>
+        <v>47140452.08</v>
       </c>
       <c r="R42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8278,13 +8545,13 @@
       <c r="T42"/>
       <c r="U42"/>
       <c r="V42" t="n">
-        <v>0.0000082</v>
+        <v>0.0000106</v>
       </c>
       <c r="W42" t="n">
-        <v>0.00000295</v>
+        <v>0.0000013</v>
       </c>
       <c r="X42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -8294,13 +8561,13 @@
       </c>
       <c r="AA42"/>
       <c r="AB42" t="n">
-        <v>0.0000028</v>
+        <v>0.00000589</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.00000104</v>
+        <v>0.0000011</v>
       </c>
       <c r="AD42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -8310,13 +8577,13 @@
       </c>
       <c r="AG42"/>
       <c r="AH42" t="n">
-        <v>-28.2781</v>
+        <v>-28.1453</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.4</v>
+        <v>1.205542</v>
       </c>
       <c r="AJ42" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="AK42" t="n">
         <v>400</v>
@@ -8331,7 +8598,7 @@
         <v>1.22</v>
       </c>
       <c r="AO42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP42" t="n">
         <v>0.68</v>
@@ -8347,7 +8614,7 @@
         <v>0.1</v>
       </c>
       <c r="AU42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV42" t="n">
         <v>1</v>
@@ -8356,7 +8623,7 @@
         <v>0</v>
       </c>
       <c r="AX42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY42" t="n">
         <v>1</v>
@@ -8365,7 +8632,7 @@
         <v>0.05</v>
       </c>
       <c r="BA42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB42" t="n">
         <v>1</v>
@@ -8374,7 +8641,7 @@
         <v>0.05</v>
       </c>
       <c r="BD42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE42" t="n">
         <v>0.2</v>
@@ -8383,7 +8650,7 @@
         <v>0.02</v>
       </c>
       <c r="BG42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH42" t="n">
         <v>0.013</v>
@@ -8392,25 +8659,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ42" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK42" s="1"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E43" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F43" t="n">
         <v>-45.527</v>
@@ -8419,31 +8686,31 @@
         <v>170.219</v>
       </c>
       <c r="H43" s="23" t="n">
-        <v>22.992</v>
+        <v>22.993</v>
       </c>
       <c r="I43" s="23"/>
       <c r="J43" s="23"/>
       <c r="K43" s="23"/>
       <c r="L43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M43" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="N43" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="O43" t="s">
+        <v>237</v>
+      </c>
+      <c r="P43" t="n">
+        <v>177777777.8</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>94280904.16</v>
+      </c>
+      <c r="R43" t="s">
         <v>205</v>
-      </c>
-      <c r="P43" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>39544734.27</v>
-      </c>
-      <c r="R43" t="s">
-        <v>206</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8451,13 +8718,13 @@
       <c r="T43"/>
       <c r="U43"/>
       <c r="V43" t="n">
-        <v>0.00000899</v>
+        <v>0.000006496</v>
       </c>
       <c r="W43" t="n">
-        <v>0.00000122</v>
+        <v>0.000000942</v>
       </c>
       <c r="X43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -8467,13 +8734,13 @@
       </c>
       <c r="AA43"/>
       <c r="AB43" t="n">
-        <v>0.00000517</v>
+        <v>0.00000229</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.00000078</v>
+        <v>0.000000453</v>
       </c>
       <c r="AD43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -8483,13 +8750,13 @@
       </c>
       <c r="AG43"/>
       <c r="AH43" t="n">
-        <v>-27.7324</v>
+        <v>-25.7265</v>
       </c>
       <c r="AI43" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ43" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK43" t="n">
         <v>400</v>
@@ -8498,13 +8765,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.86</v>
+        <v>7.51</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AO43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP43" t="n">
         <v>0.68</v>
@@ -8520,7 +8787,7 @@
         <v>0.1</v>
       </c>
       <c r="AU43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV43" t="n">
         <v>1</v>
@@ -8529,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="AX43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY43" t="n">
         <v>1</v>
@@ -8538,7 +8805,7 @@
         <v>0.05</v>
       </c>
       <c r="BA43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB43" t="n">
         <v>1</v>
@@ -8547,7 +8814,7 @@
         <v>0.05</v>
       </c>
       <c r="BD43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE43" t="n">
         <v>0.2</v>
@@ -8556,7 +8823,7 @@
         <v>0.02</v>
       </c>
       <c r="BG43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH43" t="n">
         <v>0.013</v>
@@ -8565,23 +8832,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK43" s="1"/>
     </row>
     <row r="44">
-      <c r="A44"/>
+      <c r="A44" t="s">
+        <v>256</v>
+      </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E44" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F44" t="n">
         <v>-45.527</v>
@@ -8590,85 +8859,171 @@
         <v>170.219</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>23.019</v>
+        <v>23.013</v>
       </c>
       <c r="I44" s="23"/>
-      <c r="J44" s="23" t="n">
-        <v>23.013</v>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v>23.031</v>
-      </c>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
       <c r="L44" t="s">
-        <v>200</v>
-      </c>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44"/>
-      <c r="R44"/>
-      <c r="S44"/>
+        <v>201</v>
+      </c>
+      <c r="M44" t="s">
+        <v>202</v>
+      </c>
+      <c r="N44" t="s">
+        <v>203</v>
+      </c>
+      <c r="O44" t="s">
+        <v>204</v>
+      </c>
+      <c r="P44" t="n">
+        <v>246666666.7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>19876159.8</v>
+      </c>
+      <c r="R44" t="s">
+        <v>205</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
       <c r="T44"/>
       <c r="U44"/>
-      <c r="V44"/>
-      <c r="W44"/>
-      <c r="X44"/>
-      <c r="Y44"/>
-      <c r="Z44"/>
+      <c r="V44" t="n">
+        <v>0.00001043</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.00000175</v>
+      </c>
+      <c r="X44" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
       <c r="AA44"/>
-      <c r="AB44"/>
-      <c r="AC44"/>
-      <c r="AD44"/>
-      <c r="AE44"/>
-      <c r="AF44"/>
+      <c r="AB44" t="n">
+        <v>0.00000524</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.000000979</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>206</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
       <c r="AG44"/>
-      <c r="AH44"/>
-      <c r="AI44"/>
-      <c r="AJ44"/>
-      <c r="AK44"/>
-      <c r="AL44"/>
-      <c r="AM44"/>
-      <c r="AN44"/>
-      <c r="AO44"/>
-      <c r="AP44"/>
-      <c r="AQ44"/>
+      <c r="AH44" t="n">
+        <v>-27.7962</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>400</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.000714286</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO44" t="s">
+        <v>208</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AR44"/>
-      <c r="AS44"/>
-      <c r="AT44"/>
-      <c r="AU44"/>
-      <c r="AV44"/>
-      <c r="AW44"/>
-      <c r="AX44"/>
-      <c r="AY44"/>
-      <c r="AZ44"/>
-      <c r="BA44"/>
-      <c r="BB44"/>
-      <c r="BC44"/>
-      <c r="BD44"/>
-      <c r="BE44"/>
-      <c r="BF44"/>
-      <c r="BG44"/>
-      <c r="BH44"/>
-      <c r="BI44"/>
-      <c r="BJ44"/>
+      <c r="AS44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AU44" t="s">
+        <v>209</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>210</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BA44" t="s">
+        <v>209</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BD44" t="s">
+        <v>209</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BG44" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BJ44" t="s">
+        <v>209</v>
+      </c>
       <c r="BK44" s="1"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D45" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E45" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F45" t="n">
         <v>-45.527</v>
@@ -8677,31 +9032,31 @@
         <v>170.219</v>
       </c>
       <c r="H45" s="23" t="n">
-        <v>22.992</v>
+        <v>23.013</v>
       </c>
       <c r="I45" s="23"/>
       <c r="J45" s="23"/>
       <c r="K45" s="23"/>
       <c r="L45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M45" t="s">
+        <v>217</v>
+      </c>
+      <c r="N45" t="s">
+        <v>203</v>
+      </c>
+      <c r="O45" t="s">
         <v>218</v>
       </c>
-      <c r="N45" t="s">
-        <v>204</v>
-      </c>
-      <c r="O45" t="s">
-        <v>219</v>
-      </c>
       <c r="P45" t="n">
-        <v>406666666.7</v>
+        <v>582222222.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>32960882.16</v>
+        <v>73114150.56</v>
       </c>
       <c r="R45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -8709,13 +9064,13 @@
       <c r="T45"/>
       <c r="U45"/>
       <c r="V45" t="n">
-        <v>0.00000725</v>
+        <v>0.00000606</v>
       </c>
       <c r="W45" t="n">
-        <v>0.00000101</v>
+        <v>0.00000109</v>
       </c>
       <c r="X45" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -8725,13 +9080,13 @@
       </c>
       <c r="AA45"/>
       <c r="AB45" t="n">
-        <v>0.00000388</v>
+        <v>0.00000338</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.000000546</v>
+        <v>0.000000533</v>
       </c>
       <c r="AD45" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -8741,13 +9096,13 @@
       </c>
       <c r="AG45"/>
       <c r="AH45" t="n">
-        <v>-30.1941</v>
+        <v>-27.5148</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.024978</v>
+        <v>0.088087</v>
       </c>
       <c r="AJ45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK45" t="n">
         <v>400</v>
@@ -8762,7 +9117,7 @@
         <v>1.22</v>
       </c>
       <c r="AO45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP45" t="n">
         <v>0.68</v>
@@ -8778,7 +9133,7 @@
         <v>0.1</v>
       </c>
       <c r="AU45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV45" t="n">
         <v>1</v>
@@ -8787,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="AX45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY45" t="n">
         <v>1</v>
@@ -8796,7 +9151,7 @@
         <v>0.05</v>
       </c>
       <c r="BA45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB45" t="n">
         <v>1</v>
@@ -8805,7 +9160,7 @@
         <v>0.05</v>
       </c>
       <c r="BD45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE45" t="n">
         <v>0.2</v>
@@ -8814,7 +9169,7 @@
         <v>0.02</v>
       </c>
       <c r="BG45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH45" t="n">
         <v>0.013</v>
@@ -8823,25 +9178,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ45" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK45" s="1"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F46" t="n">
         <v>-45.527</v>
@@ -8850,31 +9205,31 @@
         <v>170.219</v>
       </c>
       <c r="H46" s="23" t="n">
-        <v>22.993</v>
+        <v>23.014</v>
       </c>
       <c r="I46" s="23"/>
       <c r="J46" s="23"/>
       <c r="K46" s="23"/>
       <c r="L46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M46" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="N46" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="O46" t="s">
+        <v>237</v>
+      </c>
+      <c r="P46" t="n">
+        <v>240740740.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>50102775.03</v>
+      </c>
+      <c r="R46" t="s">
         <v>205</v>
-      </c>
-      <c r="P46" t="n">
-        <v>133333333.3</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>47140452.08</v>
-      </c>
-      <c r="R46" t="s">
-        <v>206</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -8882,13 +9237,13 @@
       <c r="T46"/>
       <c r="U46"/>
       <c r="V46" t="n">
-        <v>0.0000106</v>
+        <v>0.00000881</v>
       </c>
       <c r="W46" t="n">
-        <v>0.0000013</v>
+        <v>0.000000647</v>
       </c>
       <c r="X46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
@@ -8898,13 +9253,13 @@
       </c>
       <c r="AA46"/>
       <c r="AB46" t="n">
-        <v>0.00000589</v>
+        <v>0.000003493</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.0000011</v>
+        <v>0.000000881</v>
       </c>
       <c r="AD46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8914,13 +9269,13 @@
       </c>
       <c r="AG46"/>
       <c r="AH46" t="n">
-        <v>-28.1453</v>
+        <v>-28.0006</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.205542</v>
+        <v>1.34713</v>
       </c>
       <c r="AJ46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK46" t="n">
         <v>400</v>
@@ -8929,13 +9284,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM46" t="n">
-        <v>6.86</v>
+        <v>7.51</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AO46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP46" t="n">
         <v>0.68</v>
@@ -8951,7 +9306,7 @@
         <v>0.1</v>
       </c>
       <c r="AU46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV46" t="n">
         <v>1</v>
@@ -8960,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="AX46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY46" t="n">
         <v>1</v>
@@ -8969,7 +9324,7 @@
         <v>0.05</v>
       </c>
       <c r="BA46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB46" t="n">
         <v>1</v>
@@ -8978,7 +9333,7 @@
         <v>0.05</v>
       </c>
       <c r="BD46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE46" t="n">
         <v>0.2</v>
@@ -8987,7 +9342,7 @@
         <v>0.02</v>
       </c>
       <c r="BG46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH46" t="n">
         <v>0.013</v>
@@ -8996,25 +9351,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK46" s="1"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C47" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F47" t="n">
         <v>-45.527</v>
@@ -9023,31 +9378,31 @@
         <v>170.219</v>
       </c>
       <c r="H47" s="23" t="n">
-        <v>22.993</v>
+        <v>23.014</v>
       </c>
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
       <c r="K47" s="23"/>
       <c r="L47" t="s">
+        <v>201</v>
+      </c>
+      <c r="M47" t="s">
         <v>202</v>
       </c>
-      <c r="M47" t="s">
-        <v>236</v>
-      </c>
       <c r="N47" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="O47" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="P47" t="n">
-        <v>177777777.8</v>
+        <v>314814814.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>94280904.16</v>
+        <v>33945005.15</v>
       </c>
       <c r="R47" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9055,13 +9410,13 @@
       <c r="T47"/>
       <c r="U47"/>
       <c r="V47" t="n">
-        <v>0.000006496</v>
+        <v>0.000009713</v>
       </c>
       <c r="W47" t="n">
-        <v>0.000000942</v>
+        <v>0.00000129</v>
       </c>
       <c r="X47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -9071,13 +9426,13 @@
       </c>
       <c r="AA47"/>
       <c r="AB47" t="n">
-        <v>0.00000229</v>
+        <v>0.000004421</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.000000453</v>
+        <v>0.00000105</v>
       </c>
       <c r="AD47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -9087,13 +9442,13 @@
       </c>
       <c r="AG47"/>
       <c r="AH47" t="n">
-        <v>-25.7265</v>
+        <v>-26.4007</v>
       </c>
       <c r="AI47" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK47" t="n">
         <v>400</v>
@@ -9102,13 +9457,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM47" t="n">
-        <v>7.51</v>
+        <v>6.86</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="AO47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP47" t="n">
         <v>0.68</v>
@@ -9124,7 +9479,7 @@
         <v>0.1</v>
       </c>
       <c r="AU47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV47" t="n">
         <v>1</v>
@@ -9133,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="AX47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY47" t="n">
         <v>1</v>
@@ -9142,7 +9497,7 @@
         <v>0.05</v>
       </c>
       <c r="BA47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB47" t="n">
         <v>1</v>
@@ -9151,7 +9506,7 @@
         <v>0.05</v>
       </c>
       <c r="BD47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE47" t="n">
         <v>0.2</v>
@@ -9160,7 +9515,7 @@
         <v>0.02</v>
       </c>
       <c r="BG47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH47" t="n">
         <v>0.013</v>
@@ -9169,25 +9524,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK47" s="1"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F48" t="n">
         <v>-45.527</v>
@@ -9196,31 +9551,31 @@
         <v>170.219</v>
       </c>
       <c r="H48" s="23" t="n">
-        <v>23.013</v>
+        <v>23.014</v>
       </c>
       <c r="I48" s="23"/>
       <c r="J48" s="23"/>
       <c r="K48" s="23"/>
       <c r="L48" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" t="s">
         <v>202</v>
       </c>
-      <c r="M48" t="s">
+      <c r="N48" t="s">
         <v>203</v>
       </c>
-      <c r="N48" t="s">
+      <c r="O48" t="s">
         <v>204</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="n">
+        <v>143222222.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>41882257.06</v>
+      </c>
+      <c r="R48" t="s">
         <v>205</v>
-      </c>
-      <c r="P48" t="n">
-        <v>246666666.7</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>19876159.8</v>
-      </c>
-      <c r="R48" t="s">
-        <v>206</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9228,13 +9583,13 @@
       <c r="T48"/>
       <c r="U48"/>
       <c r="V48" t="n">
-        <v>0.00001043</v>
+        <v>0.0000125</v>
       </c>
       <c r="W48" t="n">
-        <v>0.00000175</v>
+        <v>0.0000026</v>
       </c>
       <c r="X48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -9244,13 +9599,13 @@
       </c>
       <c r="AA48"/>
       <c r="AB48" t="n">
-        <v>0.00000524</v>
+        <v>0.000002</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.000000979</v>
+        <v>0.000000782</v>
       </c>
       <c r="AD48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -9260,13 +9615,13 @@
       </c>
       <c r="AG48"/>
       <c r="AH48" t="n">
-        <v>-27.7962</v>
+        <v>-28.3259</v>
       </c>
       <c r="AI48" t="n">
         <v>0.4</v>
       </c>
       <c r="AJ48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AK48" t="n">
         <v>400</v>
@@ -9281,7 +9636,7 @@
         <v>1.22</v>
       </c>
       <c r="AO48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP48" t="n">
         <v>0.68</v>
@@ -9297,7 +9652,7 @@
         <v>0.1</v>
       </c>
       <c r="AU48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV48" t="n">
         <v>1</v>
@@ -9306,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="AX48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY48" t="n">
         <v>1</v>
@@ -9315,7 +9670,7 @@
         <v>0.05</v>
       </c>
       <c r="BA48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB48" t="n">
         <v>1</v>
@@ -9324,7 +9679,7 @@
         <v>0.05</v>
       </c>
       <c r="BD48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE48" t="n">
         <v>0.2</v>
@@ -9333,7 +9688,7 @@
         <v>0.02</v>
       </c>
       <c r="BG48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH48" t="n">
         <v>0.013</v>
@@ -9342,25 +9697,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK48" s="1"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E49" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F49" t="n">
         <v>-45.527</v>
@@ -9369,31 +9724,31 @@
         <v>170.219</v>
       </c>
       <c r="H49" s="23" t="n">
-        <v>23.013</v>
+        <v>23.031</v>
       </c>
       <c r="I49" s="23"/>
       <c r="J49" s="23"/>
       <c r="K49" s="23"/>
       <c r="L49" t="s">
+        <v>201</v>
+      </c>
+      <c r="M49" t="s">
         <v>202</v>
       </c>
-      <c r="M49" t="s">
-        <v>218</v>
-      </c>
       <c r="N49" t="s">
+        <v>203</v>
+      </c>
+      <c r="O49" t="s">
         <v>204</v>
       </c>
-      <c r="O49" t="s">
-        <v>219</v>
-      </c>
       <c r="P49" t="n">
-        <v>582222222.2</v>
+        <v>186111111.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>73114150.56</v>
+        <v>5555555.556</v>
       </c>
       <c r="R49" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -9401,13 +9756,13 @@
       <c r="T49"/>
       <c r="U49"/>
       <c r="V49" t="n">
-        <v>0.00000606</v>
+        <v>0.00000813</v>
       </c>
       <c r="W49" t="n">
-        <v>0.00000109</v>
+        <v>0.00000174</v>
       </c>
       <c r="X49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -9417,13 +9772,13 @@
       </c>
       <c r="AA49"/>
       <c r="AB49" t="n">
-        <v>0.00000338</v>
+        <v>0.000005725</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.000000533</v>
+        <v>0.00000131</v>
       </c>
       <c r="AD49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -9433,13 +9788,13 @@
       </c>
       <c r="AG49"/>
       <c r="AH49" t="n">
-        <v>-27.5148</v>
+        <v>-26.9019</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.088087</v>
+        <v>0.4</v>
       </c>
       <c r="AJ49" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK49" t="n">
         <v>400</v>
@@ -9454,7 +9809,7 @@
         <v>1.22</v>
       </c>
       <c r="AO49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP49" t="n">
         <v>0.68</v>
@@ -9470,7 +9825,7 @@
         <v>0.1</v>
       </c>
       <c r="AU49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV49" t="n">
         <v>1</v>
@@ -9479,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="AX49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY49" t="n">
         <v>1</v>
@@ -9488,7 +9843,7 @@
         <v>0.05</v>
       </c>
       <c r="BA49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB49" t="n">
         <v>1</v>
@@ -9497,7 +9852,7 @@
         <v>0.05</v>
       </c>
       <c r="BD49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE49" t="n">
         <v>0.2</v>
@@ -9506,7 +9861,7 @@
         <v>0.02</v>
       </c>
       <c r="BG49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH49" t="n">
         <v>0.013</v>
@@ -9515,25 +9870,25 @@
         <v>0.005</v>
       </c>
       <c r="BJ49" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK49" s="1"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F50" t="n">
         <v>-45.527</v>
@@ -9542,31 +9897,29 @@
         <v>170.219</v>
       </c>
       <c r="H50" s="23" t="n">
-        <v>23.014</v>
+        <v>23.031</v>
       </c>
       <c r="I50" s="23"/>
       <c r="J50" s="23"/>
       <c r="K50" s="23"/>
       <c r="L50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M50" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="N50" t="s">
-        <v>237</v>
-      </c>
-      <c r="O50" t="s">
-        <v>238</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="O50"/>
       <c r="P50" t="n">
-        <v>240740740.7</v>
+        <v>461111111.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>50102775.03</v>
+        <v>29397236.79</v>
       </c>
       <c r="R50" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -9574,13 +9927,13 @@
       <c r="T50"/>
       <c r="U50"/>
       <c r="V50" t="n">
-        <v>0.00000881</v>
+        <v>0.0000074</v>
       </c>
       <c r="W50" t="n">
-        <v>0.000000647</v>
+        <v>0.000000954</v>
       </c>
       <c r="X50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -9590,13 +9943,13 @@
       </c>
       <c r="AA50"/>
       <c r="AB50" t="n">
-        <v>0.000003493</v>
+        <v>0.00000362</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.000000881</v>
+        <v>0.000000646</v>
       </c>
       <c r="AD50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -9606,13 +9959,13 @@
       </c>
       <c r="AG50"/>
       <c r="AH50" t="n">
-        <v>-28.0006</v>
+        <v>-27.3156</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.34713</v>
+        <v>0.4</v>
       </c>
       <c r="AJ50" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK50" t="n">
         <v>400</v>
@@ -9621,13 +9974,13 @@
         <v>0.000714286</v>
       </c>
       <c r="AM50" t="n">
-        <v>7.51</v>
+        <v>7.31</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AO50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AP50" t="n">
         <v>0.68</v>
@@ -9643,7 +9996,7 @@
         <v>0.1</v>
       </c>
       <c r="AU50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AV50" t="n">
         <v>1</v>
@@ -9652,7 +10005,7 @@
         <v>0</v>
       </c>
       <c r="AX50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AY50" t="n">
         <v>1</v>
@@ -9661,7 +10014,7 @@
         <v>0.05</v>
       </c>
       <c r="BA50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BB50" t="n">
         <v>1</v>
@@ -9670,7 +10023,7 @@
         <v>0.05</v>
       </c>
       <c r="BD50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BE50" t="n">
         <v>0.2</v>
@@ -9679,7 +10032,7 @@
         <v>0.02</v>
       </c>
       <c r="BG50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BH50" t="n">
         <v>0.013</v>
@@ -9688,354 +10041,22 @@
         <v>0.005</v>
       </c>
       <c r="BJ50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BK50" s="1"/>
     </row>
     <row r="51">
-      <c r="A51" t="s">
-        <v>260</v>
-      </c>
-      <c r="B51" t="s">
-        <v>196</v>
-      </c>
-      <c r="C51" t="s">
-        <v>197</v>
-      </c>
-      <c r="D51" t="s">
-        <v>198</v>
-      </c>
-      <c r="E51" t="s">
-        <v>199</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-45.527</v>
-      </c>
-      <c r="G51" t="n">
-        <v>170.219</v>
-      </c>
-      <c r="H51" s="23" t="n">
-        <v>23.014</v>
-      </c>
+      <c r="H51" s="23"/>
       <c r="I51" s="23"/>
       <c r="J51" s="23"/>
       <c r="K51" s="23"/>
-      <c r="L51" t="s">
-        <v>202</v>
-      </c>
-      <c r="M51" t="s">
-        <v>203</v>
-      </c>
-      <c r="N51" t="s">
-        <v>204</v>
-      </c>
-      <c r="O51" t="s">
-        <v>205</v>
-      </c>
-      <c r="P51" t="n">
-        <v>314814814.8</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>33945005.15</v>
-      </c>
-      <c r="R51" t="s">
-        <v>206</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51"/>
-      <c r="U51"/>
-      <c r="V51" t="n">
-        <v>0.000009713</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0.00000129</v>
-      </c>
-      <c r="X51" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51" t="n">
-        <v>0.000004421</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0.00000105</v>
-      </c>
-      <c r="AD51" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51"/>
-      <c r="AH51" t="n">
-        <v>-26.4007</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>400</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0.000714286</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO51" t="s">
-        <v>209</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AR51"/>
-      <c r="AS51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AU51" t="s">
-        <v>210</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="s">
-        <v>211</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BA51" t="s">
-        <v>210</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BD51" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BG51" t="s">
-        <v>210</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="BJ51" t="s">
-        <v>210</v>
-      </c>
       <c r="BK51" s="1"/>
     </row>
     <row r="52">
-      <c r="A52" t="s">
-        <v>261</v>
-      </c>
-      <c r="B52" t="s">
-        <v>196</v>
-      </c>
-      <c r="C52" t="s">
-        <v>197</v>
-      </c>
-      <c r="D52" t="s">
-        <v>198</v>
-      </c>
-      <c r="E52" t="s">
-        <v>199</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-45.527</v>
-      </c>
-      <c r="G52" t="n">
-        <v>170.219</v>
-      </c>
-      <c r="H52" s="23" t="n">
-        <v>23.014</v>
-      </c>
+      <c r="H52" s="23"/>
       <c r="I52" s="23"/>
       <c r="J52" s="23"/>
       <c r="K52" s="23"/>
-      <c r="L52" t="s">
-        <v>202</v>
-      </c>
-      <c r="M52" t="s">
-        <v>203</v>
-      </c>
-      <c r="N52" t="s">
-        <v>204</v>
-      </c>
-      <c r="O52" t="s">
-        <v>205</v>
-      </c>
-      <c r="P52" t="n">
-        <v>143222222.2</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>41882257.06</v>
-      </c>
-      <c r="R52" t="s">
-        <v>206</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52"/>
-      <c r="U52"/>
-      <c r="V52" t="n">
-        <v>0.0000125</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0.0000026</v>
-      </c>
-      <c r="X52" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52"/>
-      <c r="AB52" t="n">
-        <v>0.000002</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.000000782</v>
-      </c>
-      <c r="AD52" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52"/>
-      <c r="AH52" t="n">
-        <v>-28.3259</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AJ52" t="s">
-        <v>214</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>400</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0.000714286</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO52" t="s">
-        <v>209</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AR52"/>
-      <c r="AS52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AU52" t="s">
-        <v>210</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="s">
-        <v>211</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BA52" t="s">
-        <v>210</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BD52" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BG52" t="s">
-        <v>210</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="BJ52" t="s">
-        <v>210</v>
-      </c>
       <c r="BK52" s="1"/>
     </row>
     <row r="53">
